--- a/Data/2009_F033_CO_RSIS/2009_F033_CO_RSIS_PlantAnalysis.xlsx
+++ b/Data/2009_F033_CO_RSIS/2009_F033_CO_RSIS_PlantAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2009_F033_CO_RSIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7FBBD446-C319-4809-81E2-9BDEE53016FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889E76F3-4E1D-4519-806E-A9E73FA497FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-24255" windowWidth="17085" windowHeight="23025" xr2:uid="{4B356D3E-B333-4106-8E36-938C349600A6}"/>
+    <workbookView xWindow="-1320" yWindow="-27630" windowWidth="17655" windowHeight="15615" xr2:uid="{4B356D3E-B333-4106-8E36-938C349600A6}"/>
   </bookViews>
   <sheets>
     <sheet name="PlantDF" sheetId="17" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="120">
   <si>
     <t>Plant Samples</t>
   </si>
@@ -659,16 +659,19 @@
   <si>
     <t>p15-S4</t>
   </si>
+  <si>
+    <t>LAID_LAB</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="164" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="45" x14ac:knownFonts="1">
     <font>
@@ -1736,7 +1739,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1752,7 +1755,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="15" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -1768,7 +1770,7 @@
     <xf numFmtId="0" fontId="29" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1792,10 +1794,10 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1846,8 +1848,8 @@
     <xf numFmtId="2" fontId="6" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1856,16 +1858,16 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="37" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1950,11 +1952,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -1965,11 +1971,6 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2757,7 +2758,7 @@
         <v>82</v>
       </c>
       <c r="Q1" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -2767,7 +2768,7 @@
       <c r="B2">
         <v>161</v>
       </c>
-      <c r="C2" s="85">
+      <c r="C2" s="80">
         <v>39974</v>
       </c>
       <c r="D2" t="s">
@@ -2776,40 +2777,40 @@
       <c r="E2">
         <v>42</v>
       </c>
-      <c r="F2" s="86">
+      <c r="F2" s="81">
         <v>3.75</v>
       </c>
-      <c r="G2" s="86">
+      <c r="G2" s="81">
         <v>0</v>
       </c>
-      <c r="H2" s="86">
+      <c r="H2" s="81">
         <v>0</v>
       </c>
-      <c r="I2" s="86">
+      <c r="I2" s="81">
         <v>0</v>
       </c>
-      <c r="J2" s="87">
+      <c r="J2" s="82">
         <v>3.9350000000000001</v>
       </c>
-      <c r="K2" s="87">
+      <c r="K2" s="82">
         <v>3.9975000000000001</v>
       </c>
-      <c r="L2" s="87">
+      <c r="L2" s="82">
         <v>9.057380952380953</v>
       </c>
-      <c r="M2" s="86">
+      <c r="M2" s="81">
         <v>833.91092104072629</v>
       </c>
-      <c r="N2" s="86">
+      <c r="N2" s="81">
         <v>847.15601190859036</v>
       </c>
-      <c r="O2" s="86">
+      <c r="O2" s="81">
         <v>10.066269059576745</v>
       </c>
-      <c r="P2" s="86">
+      <c r="P2" s="81">
         <v>1691.1332020088935</v>
       </c>
-      <c r="Q2" s="88">
+      <c r="Q2" s="83">
         <v>1.2700187829560208</v>
       </c>
     </row>
@@ -2820,7 +2821,7 @@
       <c r="B3">
         <v>161</v>
       </c>
-      <c r="C3" s="85">
+      <c r="C3" s="80">
         <v>39974</v>
       </c>
       <c r="D3" t="s">
@@ -2829,40 +2830,40 @@
       <c r="E3">
         <v>43</v>
       </c>
-      <c r="F3" s="86">
+      <c r="F3" s="81">
         <v>3.125</v>
       </c>
-      <c r="G3" s="86">
+      <c r="G3" s="81">
         <v>0</v>
       </c>
-      <c r="H3" s="86">
+      <c r="H3" s="81">
         <v>0</v>
       </c>
-      <c r="I3" s="86">
+      <c r="I3" s="81">
         <v>0</v>
       </c>
-      <c r="J3" s="87">
+      <c r="J3" s="82">
         <v>4.0724999999999998</v>
       </c>
-      <c r="K3" s="87">
+      <c r="K3" s="82">
         <v>4.1637500000000003</v>
       </c>
-      <c r="L3" s="87">
+      <c r="L3" s="82">
         <v>8.720930232558139</v>
       </c>
-      <c r="M3" s="86">
+      <c r="M3" s="81">
         <v>819.01189114628812</v>
       </c>
-      <c r="N3" s="86">
+      <c r="N3" s="81">
         <v>837.36298631316333</v>
       </c>
-      <c r="O3" s="86">
+      <c r="O3" s="81">
         <v>6.536006497791127</v>
       </c>
-      <c r="P3" s="86">
+      <c r="P3" s="81">
         <v>1662.9108839572427</v>
       </c>
-      <c r="Q3" s="88">
+      <c r="Q3" s="83">
         <v>1.2857958782779595</v>
       </c>
     </row>
@@ -2873,7 +2874,7 @@
       <c r="B4">
         <v>161</v>
       </c>
-      <c r="C4" s="85">
+      <c r="C4" s="80">
         <v>39974</v>
       </c>
       <c r="D4" t="s">
@@ -2882,40 +2883,40 @@
       <c r="E4">
         <v>45</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="81">
         <v>3.5</v>
       </c>
-      <c r="G4" s="86">
+      <c r="G4" s="81">
         <v>0</v>
       </c>
-      <c r="H4" s="86">
+      <c r="H4" s="81">
         <v>0</v>
       </c>
-      <c r="I4" s="86">
+      <c r="I4" s="81">
         <v>0</v>
       </c>
-      <c r="J4" s="87">
+      <c r="J4" s="82">
         <v>3.8675000000000002</v>
       </c>
-      <c r="K4" s="87">
+      <c r="K4" s="82">
         <v>3.88375</v>
       </c>
-      <c r="L4" s="87">
+      <c r="L4" s="82">
         <v>7.923333333333332</v>
       </c>
-      <c r="M4" s="86">
+      <c r="M4" s="81">
         <v>787.75073229128145</v>
       </c>
-      <c r="N4" s="86">
+      <c r="N4" s="81">
         <v>791.06060931771549</v>
       </c>
-      <c r="O4" s="86">
+      <c r="O4" s="81">
         <v>6.6197540528679113</v>
       </c>
-      <c r="P4" s="86">
+      <c r="P4" s="81">
         <v>1585.4310956618647</v>
       </c>
-      <c r="Q4" s="88">
+      <c r="Q4" s="83">
         <v>1.2213191621616186</v>
       </c>
     </row>
@@ -2926,7 +2927,7 @@
       <c r="B5">
         <v>161</v>
       </c>
-      <c r="C5" s="85">
+      <c r="C5" s="80">
         <v>39974</v>
       </c>
       <c r="D5" t="s">
@@ -2935,40 +2936,40 @@
       <c r="E5">
         <v>45</v>
       </c>
-      <c r="F5" s="86">
+      <c r="F5" s="81">
         <v>2.875</v>
       </c>
-      <c r="G5" s="86">
+      <c r="G5" s="81">
         <v>0</v>
       </c>
-      <c r="H5" s="86">
+      <c r="H5" s="81">
         <v>0</v>
       </c>
-      <c r="I5" s="86">
+      <c r="I5" s="81">
         <v>0</v>
       </c>
-      <c r="J5" s="87">
+      <c r="J5" s="82">
         <v>0.43375000000000002</v>
       </c>
-      <c r="K5" s="87">
+      <c r="K5" s="82">
         <v>4.1612499999999999</v>
       </c>
-      <c r="L5" s="87">
+      <c r="L5" s="82">
         <v>8.2731111111111133</v>
       </c>
-      <c r="M5" s="86">
+      <c r="M5" s="81">
         <v>143.29573320042095</v>
       </c>
-      <c r="N5" s="86">
+      <c r="N5" s="81">
         <v>1374.7305355164306</v>
       </c>
-      <c r="O5" s="86">
+      <c r="O5" s="81">
         <v>16.93119614183648</v>
       </c>
-      <c r="P5" s="86">
+      <c r="P5" s="81">
         <v>1534.9574648586877</v>
       </c>
-      <c r="Q5" s="88">
+      <c r="Q5" s="83">
         <v>2.1858711061915401</v>
       </c>
     </row>
@@ -2979,7 +2980,7 @@
       <c r="B6">
         <v>161</v>
       </c>
-      <c r="C6" s="85">
+      <c r="C6" s="80">
         <v>39974</v>
       </c>
       <c r="D6" t="s">
@@ -2988,40 +2989,40 @@
       <c r="E6">
         <v>40</v>
       </c>
-      <c r="F6" s="86">
+      <c r="F6" s="81">
         <v>2.75</v>
       </c>
-      <c r="G6" s="86">
+      <c r="G6" s="81">
         <v>0</v>
       </c>
-      <c r="H6" s="86">
+      <c r="H6" s="81">
         <v>0</v>
       </c>
-      <c r="I6" s="86">
+      <c r="I6" s="81">
         <v>0</v>
       </c>
-      <c r="J6" s="87">
+      <c r="J6" s="82">
         <v>4.0112500000000004</v>
       </c>
-      <c r="K6" s="87">
+      <c r="K6" s="82">
         <v>3.7362500000000001</v>
       </c>
-      <c r="L6" s="87">
+      <c r="L6" s="82">
         <v>8.2919999999999998</v>
       </c>
-      <c r="M6" s="86">
+      <c r="M6" s="81">
         <v>763.5016132936064</v>
       </c>
-      <c r="N6" s="86">
+      <c r="N6" s="81">
         <v>711.15809352900885</v>
       </c>
-      <c r="O6" s="86">
+      <c r="O6" s="81">
         <v>5.7102021561379104</v>
       </c>
-      <c r="P6" s="86">
+      <c r="P6" s="81">
         <v>1480.3699089787533</v>
       </c>
-      <c r="Q6" s="88">
+      <c r="Q6" s="83">
         <v>1.1442721685702728</v>
       </c>
     </row>
@@ -3032,7 +3033,7 @@
       <c r="B7">
         <v>161</v>
       </c>
-      <c r="C7" s="85">
+      <c r="C7" s="80">
         <v>39974</v>
       </c>
       <c r="D7" t="s">
@@ -3041,40 +3042,40 @@
       <c r="E7">
         <v>40</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="81">
         <v>3.375</v>
       </c>
-      <c r="G7" s="86">
+      <c r="G7" s="81">
         <v>0</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H7" s="81">
         <v>0</v>
       </c>
-      <c r="I7" s="86">
+      <c r="I7" s="81">
         <v>0</v>
       </c>
-      <c r="J7" s="87">
+      <c r="J7" s="82">
         <v>4.41</v>
       </c>
-      <c r="K7" s="87">
+      <c r="K7" s="82">
         <v>4.16</v>
       </c>
-      <c r="L7" s="87">
+      <c r="L7" s="82">
         <v>9.343</v>
       </c>
-      <c r="M7" s="86">
+      <c r="M7" s="81">
         <v>854.47967652692057</v>
       </c>
-      <c r="N7" s="86">
+      <c r="N7" s="81">
         <v>806.03978556734455</v>
       </c>
-      <c r="O7" s="86">
+      <c r="O7" s="81">
         <v>11.141174920702479</v>
       </c>
-      <c r="P7" s="86">
+      <c r="P7" s="81">
         <v>1671.6606370149675</v>
       </c>
-      <c r="Q7" s="88">
+      <c r="Q7" s="83">
         <v>1.2793338501606217</v>
       </c>
     </row>
@@ -3085,7 +3086,7 @@
       <c r="B8">
         <v>161</v>
       </c>
-      <c r="C8" s="85">
+      <c r="C8" s="80">
         <v>39974</v>
       </c>
       <c r="D8" t="s">
@@ -3094,40 +3095,40 @@
       <c r="E8">
         <v>36</v>
       </c>
-      <c r="F8" s="86">
+      <c r="F8" s="81">
         <v>3.5</v>
       </c>
-      <c r="G8" s="86">
+      <c r="G8" s="81">
         <v>0</v>
       </c>
-      <c r="H8" s="86">
+      <c r="H8" s="81">
         <v>0</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="81">
         <v>0</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="82">
         <v>4.9137500000000003</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="82">
         <v>5.0537500000000009</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="82">
         <v>9.9427777777777777</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="81">
         <v>785.72446025172178</v>
       </c>
-      <c r="N8" s="86">
+      <c r="N8" s="81">
         <v>808.11091142144801</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="81">
         <v>12.192620726368617</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="81">
         <v>1606.0279923995383</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="83">
         <v>1.1065602825292722</v>
       </c>
     </row>
@@ -3138,7 +3139,7 @@
       <c r="B9">
         <v>161</v>
       </c>
-      <c r="C9" s="85">
+      <c r="C9" s="80">
         <v>39974</v>
       </c>
       <c r="D9" t="s">
@@ -3147,40 +3148,40 @@
       <c r="E9">
         <v>34</v>
       </c>
-      <c r="F9" s="86">
+      <c r="F9" s="81">
         <v>4.25</v>
       </c>
-      <c r="G9" s="86">
+      <c r="G9" s="81">
         <v>0</v>
       </c>
-      <c r="H9" s="86">
+      <c r="H9" s="81">
         <v>0</v>
       </c>
-      <c r="I9" s="86">
+      <c r="I9" s="81">
         <v>0</v>
       </c>
-      <c r="J9" s="87">
+      <c r="J9" s="82">
         <v>5.2137500000000001</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="82">
         <v>5.2774999999999999</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="82">
         <v>11.491764705882352</v>
       </c>
-      <c r="M9" s="86">
+      <c r="M9" s="81">
         <v>865.64843124295464</v>
       </c>
-      <c r="N9" s="86">
+      <c r="N9" s="81">
         <v>876.23296013132438</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="81">
         <v>19.301199737615626</v>
       </c>
-      <c r="P9" s="86">
+      <c r="P9" s="81">
         <v>1761.1825911118949</v>
       </c>
-      <c r="Q9" s="88">
+      <c r="Q9" s="83">
         <v>1.3478878689883704</v>
       </c>
     </row>
@@ -3191,7 +3192,7 @@
       <c r="B10">
         <v>188</v>
       </c>
-      <c r="C10" s="85">
+      <c r="C10" s="80">
         <v>40001</v>
       </c>
       <c r="D10" t="s">
@@ -3200,40 +3201,40 @@
       <c r="E10">
         <v>21</v>
       </c>
-      <c r="F10" s="86">
+      <c r="F10" s="81">
         <v>11.875</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="81">
         <v>0.375</v>
       </c>
-      <c r="H10" s="86">
+      <c r="H10" s="81">
         <v>2.625</v>
       </c>
-      <c r="I10" s="86">
+      <c r="I10" s="81">
         <v>0</v>
       </c>
-      <c r="J10" s="87">
+      <c r="J10" s="82">
         <v>10.356249999999999</v>
       </c>
-      <c r="K10" s="87">
+      <c r="K10" s="82">
         <v>13.385000000000002</v>
       </c>
-      <c r="L10" s="87">
+      <c r="L10" s="82">
         <v>27.226190476190482</v>
       </c>
-      <c r="M10" s="86">
+      <c r="M10" s="81">
         <v>2246.9162081396453</v>
       </c>
-      <c r="N10" s="86">
+      <c r="N10" s="81">
         <v>2904.0408879612942</v>
       </c>
-      <c r="O10" s="86">
+      <c r="O10" s="81">
         <v>476.50353382032063</v>
       </c>
-      <c r="P10" s="86">
+      <c r="P10" s="81">
         <v>5627.4606299212601</v>
       </c>
-      <c r="Q10" s="88">
+      <c r="Q10" s="83">
         <v>4.5919129529930753</v>
       </c>
     </row>
@@ -3244,7 +3245,7 @@
       <c r="B11">
         <v>188</v>
       </c>
-      <c r="C11" s="85">
+      <c r="C11" s="80">
         <v>40001</v>
       </c>
       <c r="D11" t="s">
@@ -3253,40 +3254,40 @@
       <c r="E11">
         <v>4</v>
       </c>
-      <c r="F11" s="86">
+      <c r="F11" s="81">
         <v>15.375</v>
       </c>
-      <c r="G11" s="86">
+      <c r="G11" s="81">
         <v>0.5</v>
       </c>
-      <c r="H11" s="86">
+      <c r="H11" s="81">
         <v>1.875</v>
       </c>
-      <c r="I11" s="86">
+      <c r="I11" s="81">
         <v>0</v>
       </c>
-      <c r="J11" s="87">
+      <c r="J11" s="82">
         <v>13.327500000000001</v>
       </c>
-      <c r="K11" s="87">
+      <c r="K11" s="82">
         <v>17.185000000000002</v>
       </c>
-      <c r="L11" s="87">
+      <c r="L11" s="82">
         <v>142.85250000000002</v>
       </c>
-      <c r="M11" s="86">
+      <c r="M11" s="81">
         <v>2304.635278641018</v>
       </c>
-      <c r="N11" s="86">
+      <c r="N11" s="81">
         <v>2971.6869077805964</v>
       </c>
-      <c r="O11" s="86">
+      <c r="O11" s="81">
         <v>347.79198680673397</v>
       </c>
-      <c r="P11" s="86">
+      <c r="P11" s="81">
         <v>5624.1141732283477</v>
       </c>
-      <c r="Q11" s="88">
+      <c r="Q11" s="83">
         <v>4.57806654782559</v>
       </c>
     </row>
@@ -3297,7 +3298,7 @@
       <c r="B12">
         <v>188</v>
       </c>
-      <c r="C12" s="85">
+      <c r="C12" s="80">
         <v>40001</v>
       </c>
       <c r="D12" t="s">
@@ -3306,40 +3307,40 @@
       <c r="E12">
         <v>18</v>
       </c>
-      <c r="F12" s="86">
+      <c r="F12" s="81">
         <v>12.875</v>
       </c>
-      <c r="G12" s="86">
+      <c r="G12" s="81">
         <v>0.625</v>
       </c>
-      <c r="H12" s="86">
+      <c r="H12" s="81">
         <v>3</v>
       </c>
-      <c r="I12" s="86">
+      <c r="I12" s="81">
         <v>0</v>
       </c>
-      <c r="J12" s="87">
+      <c r="J12" s="82">
         <v>12.03125</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="82">
         <v>14.85</v>
       </c>
-      <c r="L12" s="87">
+      <c r="L12" s="82">
         <v>26.950000000000003</v>
       </c>
-      <c r="M12" s="86">
+      <c r="M12" s="81">
         <v>1948.6742835907758</v>
       </c>
-      <c r="N12" s="86">
+      <c r="N12" s="81">
         <v>2405.2208300320431</v>
       </c>
-      <c r="O12" s="86">
+      <c r="O12" s="81">
         <v>420.71118558977997</v>
       </c>
-      <c r="P12" s="86">
+      <c r="P12" s="81">
         <v>4774.606299212599</v>
       </c>
-      <c r="Q12" s="88">
+      <c r="Q12" s="83">
         <v>3.8253032950967953</v>
       </c>
     </row>
@@ -3350,7 +3351,7 @@
       <c r="B13">
         <v>188</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="80">
         <v>40001</v>
       </c>
       <c r="D13" t="s">
@@ -3359,40 +3360,40 @@
       <c r="E13">
         <v>19</v>
       </c>
-      <c r="F13" s="86">
+      <c r="F13" s="81">
         <v>15.875</v>
       </c>
-      <c r="G13" s="86">
+      <c r="G13" s="81">
         <v>0.75</v>
       </c>
-      <c r="H13" s="86">
+      <c r="H13" s="81">
         <v>1.75</v>
       </c>
-      <c r="I13" s="86">
+      <c r="I13" s="81">
         <v>0</v>
       </c>
-      <c r="J13" s="87">
+      <c r="J13" s="82">
         <v>12.442500000000001</v>
       </c>
-      <c r="K13" s="87">
+      <c r="K13" s="82">
         <v>16.29</v>
       </c>
-      <c r="L13" s="87">
+      <c r="L13" s="82">
         <v>31.687368421052636</v>
       </c>
-      <c r="M13" s="86">
+      <c r="M13" s="81">
         <v>2372.9849859305464</v>
       </c>
-      <c r="N13" s="86">
+      <c r="N13" s="81">
         <v>3106.765153370191</v>
       </c>
-      <c r="O13" s="86">
+      <c r="O13" s="81">
         <v>446.03726227406594</v>
       </c>
-      <c r="P13" s="86">
+      <c r="P13" s="81">
         <v>5925.7874015748039</v>
       </c>
-      <c r="Q13" s="88">
+      <c r="Q13" s="83">
         <v>4.6152865371024623</v>
       </c>
     </row>
@@ -3403,7 +3404,7 @@
       <c r="B14">
         <v>188</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="80">
         <v>40001</v>
       </c>
       <c r="D14" t="s">
@@ -3412,40 +3413,40 @@
       <c r="E14">
         <v>23</v>
       </c>
-      <c r="F14" s="86">
+      <c r="F14" s="81">
         <v>10.5</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="81">
         <v>0.375</v>
       </c>
-      <c r="H14" s="86">
+      <c r="H14" s="81">
         <v>1.5</v>
       </c>
-      <c r="I14" s="86">
+      <c r="I14" s="81">
         <v>0</v>
       </c>
-      <c r="J14" s="87">
+      <c r="J14" s="82">
         <v>9.7912499999999998</v>
       </c>
-      <c r="K14" s="87">
+      <c r="K14" s="82">
         <v>11.22625</v>
       </c>
-      <c r="L14" s="87">
+      <c r="L14" s="82">
         <v>24.945217391304354</v>
       </c>
-      <c r="M14" s="86">
+      <c r="M14" s="81">
         <v>2435.4873396648018</v>
       </c>
-      <c r="N14" s="86">
+      <c r="N14" s="81">
         <v>2792.4309712153186</v>
       </c>
-      <c r="O14" s="86">
+      <c r="O14" s="81">
         <v>419.12893321436911</v>
       </c>
-      <c r="P14" s="86">
+      <c r="P14" s="81">
         <v>5647.0472440944895</v>
       </c>
-      <c r="Q14" s="88">
+      <c r="Q14" s="83">
         <v>4.2100506376556757</v>
       </c>
     </row>
@@ -3456,7 +3457,7 @@
       <c r="B15">
         <v>188</v>
       </c>
-      <c r="C15" s="85">
+      <c r="C15" s="80">
         <v>40001</v>
       </c>
       <c r="D15" t="s">
@@ -3465,40 +3466,40 @@
       <c r="E15">
         <v>24</v>
       </c>
-      <c r="F15" s="86">
+      <c r="F15" s="81">
         <v>9.75</v>
       </c>
-      <c r="G15" s="86">
+      <c r="G15" s="81">
         <v>0.25</v>
       </c>
-      <c r="H15" s="86">
+      <c r="H15" s="81">
         <v>2.375</v>
       </c>
-      <c r="I15" s="86">
+      <c r="I15" s="81">
         <v>0</v>
       </c>
-      <c r="J15" s="87">
+      <c r="J15" s="82">
         <v>10.0725</v>
       </c>
-      <c r="K15" s="87">
+      <c r="K15" s="82">
         <v>12.52375</v>
       </c>
-      <c r="L15" s="87">
+      <c r="L15" s="82">
         <v>25.665833333333328</v>
       </c>
-      <c r="M15" s="86">
+      <c r="M15" s="81">
         <v>2528.8060629798979</v>
       </c>
-      <c r="N15" s="86">
+      <c r="N15" s="81">
         <v>3144.2179132533629</v>
       </c>
-      <c r="O15" s="86">
+      <c r="O15" s="81">
         <v>389.7712993572888</v>
       </c>
-      <c r="P15" s="86">
+      <c r="P15" s="81">
         <v>6062.7952755905499</v>
       </c>
-      <c r="Q15" s="88">
+      <c r="Q15" s="83">
         <v>4.7586399651234768</v>
       </c>
     </row>
@@ -3509,7 +3510,7 @@
       <c r="B16">
         <v>188</v>
       </c>
-      <c r="C16" s="85">
+      <c r="C16" s="80">
         <v>40001</v>
       </c>
       <c r="D16" t="s">
@@ -3518,40 +3519,40 @@
       <c r="E16">
         <v>19</v>
       </c>
-      <c r="F16" s="86">
+      <c r="F16" s="81">
         <v>16</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="81">
         <v>0.875</v>
       </c>
-      <c r="H16" s="86">
+      <c r="H16" s="81">
         <v>3.875</v>
       </c>
-      <c r="I16" s="86">
+      <c r="I16" s="81">
         <v>0</v>
       </c>
-      <c r="J16" s="87">
+      <c r="J16" s="82">
         <v>14.54875</v>
       </c>
-      <c r="K16" s="87">
+      <c r="K16" s="82">
         <v>18.445</v>
       </c>
-      <c r="L16" s="87">
+      <c r="L16" s="82">
         <v>35.533157894736839</v>
       </c>
-      <c r="M16" s="86">
+      <c r="M16" s="81">
         <v>2604.2469488122688</v>
       </c>
-      <c r="N16" s="86">
+      <c r="N16" s="81">
         <v>3301.6812420889969</v>
       </c>
-      <c r="O16" s="86">
+      <c r="O16" s="81">
         <v>739.05212405936277</v>
       </c>
-      <c r="P16" s="86">
+      <c r="P16" s="81">
         <v>6644.9803149606287</v>
       </c>
-      <c r="Q16" s="88">
+      <c r="Q16" s="83">
         <v>4.2537830969886867</v>
       </c>
     </row>
@@ -3562,7 +3563,7 @@
       <c r="B17">
         <v>188</v>
       </c>
-      <c r="C17" s="85">
+      <c r="C17" s="80">
         <v>40001</v>
       </c>
       <c r="D17" t="s">
@@ -3571,40 +3572,40 @@
       <c r="E17">
         <v>28</v>
       </c>
-      <c r="F17" s="86">
+      <c r="F17" s="81">
         <v>9.125</v>
       </c>
-      <c r="G17" s="86">
+      <c r="G17" s="81">
         <v>0.75</v>
       </c>
-      <c r="H17" s="86">
+      <c r="H17" s="81">
         <v>2.75</v>
       </c>
-      <c r="I17" s="86">
+      <c r="I17" s="81">
         <v>0</v>
       </c>
-      <c r="J17" s="87">
+      <c r="J17" s="82">
         <v>9.8837499999999991</v>
       </c>
-      <c r="K17" s="87">
+      <c r="K17" s="82">
         <v>11.471250000000001</v>
       </c>
-      <c r="L17" s="87">
+      <c r="L17" s="82">
         <v>24.139642857142857</v>
       </c>
-      <c r="M17" s="86">
+      <c r="M17" s="81">
         <v>2743.5749594143008</v>
       </c>
-      <c r="N17" s="86">
+      <c r="N17" s="81">
         <v>3184.2402178506441</v>
       </c>
-      <c r="O17" s="86">
+      <c r="O17" s="81">
         <v>724.84230305001574</v>
       </c>
-      <c r="P17" s="86">
+      <c r="P17" s="81">
         <v>6652.6574803149606</v>
       </c>
-      <c r="Q17" s="88">
+      <c r="Q17" s="83">
         <v>5.1089446235191289</v>
       </c>
     </row>
@@ -3615,7 +3616,7 @@
       <c r="B18">
         <v>222</v>
       </c>
-      <c r="C18" s="85">
+      <c r="C18" s="80">
         <v>40035</v>
       </c>
       <c r="D18" t="s">
@@ -3624,40 +3625,40 @@
       <c r="E18">
         <v>19</v>
       </c>
-      <c r="F18" s="86">
+      <c r="F18" s="81">
         <v>2.375</v>
       </c>
-      <c r="G18" s="86">
+      <c r="G18" s="81">
         <v>0.25</v>
       </c>
-      <c r="H18" s="86">
+      <c r="H18" s="81">
         <v>8.125</v>
       </c>
-      <c r="I18" s="86">
+      <c r="I18" s="81">
         <v>0</v>
       </c>
-      <c r="J18" s="87">
+      <c r="J18" s="82">
         <v>17.78875</v>
       </c>
-      <c r="K18" s="87">
+      <c r="K18" s="82">
         <v>25.65625</v>
       </c>
-      <c r="L18" s="87">
+      <c r="L18" s="82">
         <v>66.422631578947374</v>
       </c>
-      <c r="M18" s="86">
+      <c r="M18" s="81">
         <v>3364.1859527229385</v>
       </c>
-      <c r="N18" s="86">
+      <c r="N18" s="81">
         <v>4852.0776248779639</v>
       </c>
-      <c r="O18" s="86">
+      <c r="O18" s="81">
         <v>4205.2915405093345</v>
       </c>
-      <c r="P18" s="86">
+      <c r="P18" s="81">
         <v>12421.555118110238</v>
       </c>
-      <c r="Q18" s="88">
+      <c r="Q18" s="83">
         <v>5.8439013910086812</v>
       </c>
     </row>
@@ -3668,7 +3669,7 @@
       <c r="B19">
         <v>222</v>
       </c>
-      <c r="C19" s="85">
+      <c r="C19" s="80">
         <v>40035</v>
       </c>
       <c r="D19" t="s">
@@ -3677,40 +3678,40 @@
       <c r="E19">
         <v>20</v>
       </c>
-      <c r="F19" s="86">
+      <c r="F19" s="81">
         <v>12.25</v>
       </c>
-      <c r="G19" s="86">
+      <c r="G19" s="81">
         <v>0.625</v>
       </c>
-      <c r="H19" s="86">
+      <c r="H19" s="81">
         <v>7.25</v>
       </c>
-      <c r="I19" s="86">
+      <c r="I19" s="81">
         <v>0</v>
       </c>
-      <c r="J19" s="87">
+      <c r="J19" s="82">
         <v>20.411249999999999</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="82">
         <v>27.65</v>
       </c>
-      <c r="L19" s="87">
+      <c r="L19" s="82">
         <v>69.98899999999999</v>
       </c>
-      <c r="M19" s="86">
+      <c r="M19" s="81">
         <v>4161.7283134643958</v>
       </c>
-      <c r="N19" s="86">
+      <c r="N19" s="81">
         <v>5637.6649086797979</v>
       </c>
-      <c r="O19" s="86">
+      <c r="O19" s="81">
         <v>3977.9689825802129</v>
       </c>
-      <c r="P19" s="86">
+      <c r="P19" s="81">
         <v>13777.362204724408</v>
       </c>
-      <c r="Q19" s="88">
+      <c r="Q19" s="83">
         <v>7.2051345497949866</v>
       </c>
     </row>
@@ -3721,7 +3722,7 @@
       <c r="B20">
         <v>222</v>
       </c>
-      <c r="C20" s="85">
+      <c r="C20" s="80">
         <v>40035</v>
       </c>
       <c r="D20" t="s">
@@ -3730,40 +3731,40 @@
       <c r="E20">
         <v>24</v>
       </c>
-      <c r="F20" s="86">
+      <c r="F20" s="81">
         <v>3.25</v>
       </c>
-      <c r="G20" s="86">
+      <c r="G20" s="81">
         <v>0</v>
       </c>
-      <c r="H20" s="86">
+      <c r="H20" s="81">
         <v>7.875</v>
       </c>
-      <c r="I20" s="86">
+      <c r="I20" s="81">
         <v>0</v>
       </c>
-      <c r="J20" s="87">
+      <c r="J20" s="82">
         <v>19.227499999999999</v>
       </c>
-      <c r="K20" s="87">
+      <c r="K20" s="82">
         <v>28.723749999999999</v>
       </c>
-      <c r="L20" s="87">
+      <c r="L20" s="82">
         <v>65.390416666666653</v>
       </c>
-      <c r="M20" s="86">
+      <c r="M20" s="81">
         <v>4007.4703710093199</v>
       </c>
-      <c r="N20" s="86">
+      <c r="N20" s="81">
         <v>5986.7157492798842</v>
       </c>
-      <c r="O20" s="86">
+      <c r="O20" s="81">
         <v>5452.3689978210286</v>
       </c>
-      <c r="P20" s="86">
+      <c r="P20" s="81">
         <v>15446.555118110233</v>
       </c>
-      <c r="Q20" s="88">
+      <c r="Q20" s="83">
         <v>7.6143812864199276</v>
       </c>
     </row>
@@ -3774,7 +3775,7 @@
       <c r="B21">
         <v>222</v>
       </c>
-      <c r="C21" s="85">
+      <c r="C21" s="80">
         <v>40035</v>
       </c>
       <c r="D21" t="s">
@@ -3783,40 +3784,40 @@
       <c r="E21">
         <v>21</v>
       </c>
-      <c r="F21" s="86">
+      <c r="F21" s="81">
         <v>8</v>
       </c>
-      <c r="G21" s="86">
+      <c r="G21" s="81">
         <v>0</v>
       </c>
-      <c r="H21" s="86">
+      <c r="H21" s="81">
         <v>6.625</v>
       </c>
-      <c r="I21" s="86">
+      <c r="I21" s="81">
         <v>0</v>
       </c>
-      <c r="J21" s="87">
+      <c r="J21" s="82">
         <v>22.67</v>
       </c>
-      <c r="K21" s="87">
+      <c r="K21" s="82">
         <v>32.326250000000002</v>
       </c>
-      <c r="L21" s="87">
+      <c r="L21" s="82">
         <v>71.420952380952372</v>
       </c>
-      <c r="M21" s="86">
+      <c r="M21" s="81">
         <v>4293.8052489397251</v>
       </c>
-      <c r="N21" s="86">
+      <c r="N21" s="81">
         <v>6122.7446814529239</v>
       </c>
-      <c r="O21" s="86">
+      <c r="O21" s="81">
         <v>4345.6547940167984</v>
       </c>
-      <c r="P21" s="86">
+      <c r="P21" s="81">
         <v>14762.204724409446</v>
       </c>
-      <c r="Q21" s="88">
+      <c r="Q21" s="83">
         <v>7.0741412175527705</v>
       </c>
     </row>
@@ -3827,7 +3828,7 @@
       <c r="B22">
         <v>222</v>
       </c>
-      <c r="C22" s="85">
+      <c r="C22" s="80">
         <v>40035</v>
       </c>
       <c r="D22" t="s">
@@ -3836,40 +3837,40 @@
       <c r="E22">
         <v>22</v>
       </c>
-      <c r="F22" s="86">
+      <c r="F22" s="81">
         <v>1.5</v>
       </c>
-      <c r="G22" s="86">
+      <c r="G22" s="81">
         <v>0.125</v>
       </c>
-      <c r="H22" s="86">
+      <c r="H22" s="81">
         <v>6.375</v>
       </c>
-      <c r="I22" s="86">
+      <c r="I22" s="81">
         <v>0</v>
       </c>
-      <c r="J22" s="87">
+      <c r="J22" s="82">
         <v>16.731250000000003</v>
       </c>
-      <c r="K22" s="87">
+      <c r="K22" s="82">
         <v>24.116250000000001</v>
       </c>
-      <c r="L22" s="87">
+      <c r="L22" s="82">
         <v>67.51045454545455</v>
       </c>
-      <c r="M22" s="86">
+      <c r="M22" s="81">
         <v>3958.8742089143266</v>
       </c>
-      <c r="N22" s="86">
+      <c r="N22" s="81">
         <v>5706.2801727743063</v>
       </c>
-      <c r="O22" s="86">
+      <c r="O22" s="81">
         <v>4953.2511301223913</v>
       </c>
-      <c r="P22" s="86">
+      <c r="P22" s="81">
         <v>14618.405511811023</v>
       </c>
-      <c r="Q22" s="88">
+      <c r="Q22" s="83">
         <v>6.7807041403701618</v>
       </c>
     </row>
@@ -3880,7 +3881,7 @@
       <c r="B23">
         <v>222</v>
       </c>
-      <c r="C23" s="85">
+      <c r="C23" s="80">
         <v>40035</v>
       </c>
       <c r="D23" t="s">
@@ -3889,40 +3890,40 @@
       <c r="E23">
         <v>26</v>
       </c>
-      <c r="F23" s="86">
+      <c r="F23" s="81">
         <v>3.375</v>
       </c>
-      <c r="G23" s="86">
+      <c r="G23" s="81">
         <v>0</v>
       </c>
-      <c r="H23" s="86">
+      <c r="H23" s="81">
         <v>5.5</v>
       </c>
-      <c r="I23" s="86">
+      <c r="I23" s="81">
         <v>0</v>
       </c>
-      <c r="J23" s="87">
+      <c r="J23" s="82">
         <v>18.493749999999999</v>
       </c>
-      <c r="K23" s="87">
+      <c r="K23" s="82">
         <v>29.852499999999999</v>
       </c>
-      <c r="L23" s="87">
+      <c r="L23" s="82">
         <v>65.973846153846154</v>
       </c>
-      <c r="M23" s="86">
+      <c r="M23" s="81">
         <v>4394.8383676642779</v>
       </c>
-      <c r="N23" s="86">
+      <c r="N23" s="81">
         <v>7094.1216557322259</v>
       </c>
-      <c r="O23" s="86">
+      <c r="O23" s="81">
         <v>5394.1108427452264</v>
       </c>
-      <c r="P23" s="86">
+      <c r="P23" s="81">
         <v>16883.07086614173</v>
       </c>
-      <c r="Q23" s="88">
+      <c r="Q23" s="83">
         <v>7.1869880510605721</v>
       </c>
     </row>
@@ -3933,7 +3934,7 @@
       <c r="B24">
         <v>222</v>
       </c>
-      <c r="C24" s="85">
+      <c r="C24" s="80">
         <v>40035</v>
       </c>
       <c r="D24" t="s">
@@ -3942,40 +3943,40 @@
       <c r="E24">
         <v>20</v>
       </c>
-      <c r="F24" s="86">
+      <c r="F24" s="81">
         <v>8.5</v>
       </c>
-      <c r="G24" s="86">
+      <c r="G24" s="81">
         <v>0.625</v>
       </c>
-      <c r="H24" s="86">
+      <c r="H24" s="81">
         <v>7.625</v>
       </c>
-      <c r="I24" s="86">
+      <c r="I24" s="81">
         <v>0</v>
       </c>
-      <c r="J24" s="87">
+      <c r="J24" s="82">
         <v>19.763749999999998</v>
       </c>
-      <c r="K24" s="87">
+      <c r="K24" s="82">
         <v>24.69125</v>
       </c>
-      <c r="L24" s="87">
+      <c r="L24" s="82">
         <v>77.762</v>
       </c>
-      <c r="M24" s="86">
+      <c r="M24" s="81">
         <v>4431.2602303241147</v>
       </c>
-      <c r="N24" s="86">
+      <c r="N24" s="81">
         <v>5536.0624457398171</v>
       </c>
-      <c r="O24" s="86">
+      <c r="O24" s="81">
         <v>5340.1576388966978</v>
       </c>
-      <c r="P24" s="86">
+      <c r="P24" s="81">
         <v>15307.480314960629</v>
       </c>
-      <c r="Q24" s="88">
+      <c r="Q24" s="83">
         <v>7.1790367459114037</v>
       </c>
     </row>
@@ -3986,7 +3987,7 @@
       <c r="B25">
         <v>222</v>
       </c>
-      <c r="C25" s="85">
+      <c r="C25" s="80">
         <v>40035</v>
       </c>
       <c r="D25" t="s">
@@ -3995,40 +3996,40 @@
       <c r="E25">
         <v>24</v>
       </c>
-      <c r="F25" s="86">
+      <c r="F25" s="81">
         <v>1.875</v>
       </c>
-      <c r="G25" s="86">
+      <c r="G25" s="81">
         <v>0.125</v>
       </c>
-      <c r="H25" s="86">
+      <c r="H25" s="81">
         <v>6.875</v>
       </c>
-      <c r="I25" s="86">
+      <c r="I25" s="81">
         <v>0</v>
       </c>
-      <c r="J25" s="87">
+      <c r="J25" s="82">
         <v>15.4625</v>
       </c>
-      <c r="K25" s="87">
+      <c r="K25" s="82">
         <v>23.483750000000001</v>
       </c>
-      <c r="L25" s="87">
+      <c r="L25" s="82">
         <v>59.733750000000008</v>
       </c>
-      <c r="M25" s="86">
+      <c r="M25" s="81">
         <v>3506.6063879566286</v>
       </c>
-      <c r="N25" s="86">
+      <c r="N25" s="81">
         <v>5325.6761690009034</v>
       </c>
-      <c r="O25" s="86">
+      <c r="O25" s="81">
         <v>5278.0520887117591</v>
       </c>
-      <c r="P25" s="86">
+      <c r="P25" s="81">
         <v>14110.334645669291</v>
       </c>
-      <c r="Q25" s="88">
+      <c r="Q25" s="83">
         <v>5.7067198371143668</v>
       </c>
     </row>
@@ -4039,7 +4040,7 @@
       <c r="B26">
         <v>243</v>
       </c>
-      <c r="C26" s="85">
+      <c r="C26" s="80">
         <v>40056</v>
       </c>
       <c r="D26" t="s">
@@ -4048,40 +4049,40 @@
       <c r="E26">
         <v>22</v>
       </c>
-      <c r="F26" s="86">
+      <c r="F26" s="81">
         <v>5.625</v>
       </c>
-      <c r="G26" s="86">
+      <c r="G26" s="81">
         <v>0.25</v>
       </c>
-      <c r="H26" s="86">
+      <c r="H26" s="81">
         <v>8.875</v>
       </c>
-      <c r="I26" s="86">
+      <c r="I26" s="81">
         <v>2.125</v>
       </c>
-      <c r="J26" s="87">
+      <c r="J26" s="82">
         <v>16.931249999999999</v>
       </c>
-      <c r="K26" s="87">
+      <c r="K26" s="82">
         <v>30.008749999999999</v>
       </c>
-      <c r="L26" s="87">
+      <c r="L26" s="82">
         <v>85.217727272727288</v>
       </c>
-      <c r="M26" s="86">
+      <c r="M26" s="81">
         <v>3755.9168931395748</v>
       </c>
-      <c r="N26" s="86">
+      <c r="N26" s="81">
         <v>6656.9432893024568</v>
       </c>
-      <c r="O26" s="86">
+      <c r="O26" s="81">
         <v>8039.7972978729304</v>
       </c>
-      <c r="P26" s="86">
+      <c r="P26" s="81">
         <v>18452.657480314963</v>
       </c>
-      <c r="Q26" s="88">
+      <c r="Q26" s="83">
         <v>6.7758487690327769</v>
       </c>
     </row>
@@ -4092,7 +4093,7 @@
       <c r="B27">
         <v>243</v>
       </c>
-      <c r="C27" s="85">
+      <c r="C27" s="80">
         <v>40056</v>
       </c>
       <c r="D27" t="s">
@@ -4101,40 +4102,40 @@
       <c r="E27">
         <v>18</v>
       </c>
-      <c r="F27" s="86">
+      <c r="F27" s="81">
         <v>6.25</v>
       </c>
-      <c r="G27" s="86">
+      <c r="G27" s="81">
         <v>0.125</v>
       </c>
-      <c r="H27" s="86">
+      <c r="H27" s="81">
         <v>5.125</v>
       </c>
-      <c r="I27" s="86">
+      <c r="I27" s="81">
         <v>3.625</v>
       </c>
-      <c r="J27" s="87">
+      <c r="J27" s="82">
         <v>19.72625</v>
       </c>
-      <c r="K27" s="87">
+      <c r="K27" s="82">
         <v>32.042500000000004</v>
       </c>
-      <c r="L27" s="87">
+      <c r="L27" s="82">
         <v>107.255</v>
       </c>
-      <c r="M27" s="86">
+      <c r="M27" s="81">
         <v>4102.4490281496464</v>
       </c>
-      <c r="N27" s="86">
+      <c r="N27" s="81">
         <v>6663.8475627392463</v>
       </c>
-      <c r="O27" s="86">
+      <c r="O27" s="81">
         <v>8235.5734878512649</v>
       </c>
-      <c r="P27" s="86">
+      <c r="P27" s="81">
         <v>19001.870078740158</v>
       </c>
-      <c r="Q27" s="88">
+      <c r="Q27" s="83">
         <v>7.1659679826652072</v>
       </c>
     </row>
@@ -4145,7 +4146,7 @@
       <c r="B28">
         <v>243</v>
       </c>
-      <c r="C28" s="85">
+      <c r="C28" s="80">
         <v>40056</v>
       </c>
       <c r="D28" t="s">
@@ -4154,40 +4155,40 @@
       <c r="E28">
         <v>21</v>
       </c>
-      <c r="F28" s="86">
+      <c r="F28" s="81">
         <v>9.375</v>
       </c>
-      <c r="G28" s="86">
+      <c r="G28" s="81">
         <v>0.375</v>
       </c>
-      <c r="H28" s="86">
+      <c r="H28" s="81">
         <v>7.25</v>
       </c>
-      <c r="I28" s="86">
+      <c r="I28" s="81">
         <v>2.75</v>
       </c>
-      <c r="J28" s="87">
+      <c r="J28" s="82">
         <v>18.97625</v>
       </c>
-      <c r="K28" s="87">
+      <c r="K28" s="82">
         <v>35.857500000000002</v>
       </c>
-      <c r="L28" s="87">
+      <c r="L28" s="82">
         <v>80.97</v>
       </c>
-      <c r="M28" s="86">
+      <c r="M28" s="81">
         <v>4117.1298073794487</v>
       </c>
-      <c r="N28" s="86">
+      <c r="N28" s="81">
         <v>7779.7237108548106</v>
       </c>
-      <c r="O28" s="86">
+      <c r="O28" s="81">
         <v>4839.0716786161329</v>
       </c>
-      <c r="P28" s="86">
+      <c r="P28" s="81">
         <v>16735.925196850392</v>
       </c>
-      <c r="Q28" s="88">
+      <c r="Q28" s="83">
         <v>7.5744964109972086</v>
       </c>
     </row>
@@ -4198,7 +4199,7 @@
       <c r="B29">
         <v>243</v>
       </c>
-      <c r="C29" s="85">
+      <c r="C29" s="80">
         <v>40056</v>
       </c>
       <c r="D29" t="s">
@@ -4207,40 +4208,40 @@
       <c r="E29">
         <v>19</v>
       </c>
-      <c r="F29" s="86">
+      <c r="F29" s="81">
         <v>6</v>
       </c>
-      <c r="G29" s="86">
+      <c r="G29" s="81">
         <v>0</v>
       </c>
-      <c r="H29" s="86">
+      <c r="H29" s="81">
         <v>5.5</v>
       </c>
-      <c r="I29" s="86">
+      <c r="I29" s="81">
         <v>3.375</v>
       </c>
-      <c r="J29" s="87">
+      <c r="J29" s="82">
         <v>19.498750000000001</v>
       </c>
-      <c r="K29" s="87">
+      <c r="K29" s="82">
         <v>30.953749999999999</v>
       </c>
-      <c r="L29" s="87">
+      <c r="L29" s="82">
         <v>85.369473684210519</v>
       </c>
-      <c r="M29" s="86">
+      <c r="M29" s="81">
         <v>3652.6012055859555</v>
       </c>
-      <c r="N29" s="86">
+      <c r="N29" s="81">
         <v>5798.4078244711209</v>
       </c>
-      <c r="O29" s="86">
+      <c r="O29" s="81">
         <v>6513.7547494704859</v>
       </c>
-      <c r="P29" s="86">
+      <c r="P29" s="81">
         <v>15964.76377952756</v>
       </c>
-      <c r="Q29" s="88">
+      <c r="Q29" s="83">
         <v>5.8743001622326734</v>
       </c>
     </row>
@@ -4251,7 +4252,7 @@
       <c r="B30">
         <v>243</v>
       </c>
-      <c r="C30" s="85">
+      <c r="C30" s="80">
         <v>40056</v>
       </c>
       <c r="D30" t="s">
@@ -4260,40 +4261,40 @@
       <c r="E30">
         <v>20</v>
       </c>
-      <c r="F30" s="86">
+      <c r="F30" s="81">
         <v>6.75</v>
       </c>
-      <c r="G30" s="86">
+      <c r="G30" s="81">
         <v>0.125</v>
       </c>
-      <c r="H30" s="86">
+      <c r="H30" s="81">
         <v>11</v>
       </c>
-      <c r="I30" s="86">
+      <c r="I30" s="81">
         <v>2.875</v>
       </c>
-      <c r="J30" s="87">
+      <c r="J30" s="82">
         <v>20.36</v>
       </c>
-      <c r="K30" s="87">
+      <c r="K30" s="82">
         <v>34.84375</v>
       </c>
-      <c r="L30" s="87">
+      <c r="L30" s="82">
         <v>92.393000000000015</v>
       </c>
-      <c r="M30" s="86">
+      <c r="M30" s="81">
         <v>4325.8024466225634</v>
       </c>
-      <c r="N30" s="86">
+      <c r="N30" s="81">
         <v>7403.103094278239</v>
       </c>
-      <c r="O30" s="86">
+      <c r="O30" s="81">
         <v>6458.6928842960542</v>
       </c>
-      <c r="P30" s="86">
+      <c r="P30" s="81">
         <v>18187.598425196855</v>
       </c>
-      <c r="Q30" s="88">
+      <c r="Q30" s="83">
         <v>7.4819464742100195</v>
       </c>
     </row>
@@ -4304,7 +4305,7 @@
       <c r="B31">
         <v>243</v>
       </c>
-      <c r="C31" s="85">
+      <c r="C31" s="80">
         <v>40056</v>
       </c>
       <c r="D31" t="s">
@@ -4313,40 +4314,40 @@
       <c r="E31">
         <v>21</v>
       </c>
-      <c r="F31" s="86">
+      <c r="F31" s="81">
         <v>6.375</v>
       </c>
-      <c r="G31" s="86">
+      <c r="G31" s="81">
         <v>0.125</v>
       </c>
-      <c r="H31" s="86">
+      <c r="H31" s="81">
         <v>8.5</v>
       </c>
-      <c r="I31" s="86">
+      <c r="I31" s="81">
         <v>3.625</v>
       </c>
-      <c r="J31" s="87">
+      <c r="J31" s="82">
         <v>21.682500000000001</v>
       </c>
-      <c r="K31" s="87">
+      <c r="K31" s="82">
         <v>43.217500000000001</v>
       </c>
-      <c r="L31" s="87">
+      <c r="L31" s="82">
         <v>97.619523809523827</v>
       </c>
-      <c r="M31" s="86">
+      <c r="M31" s="81">
         <v>4308.5830401773328</v>
       </c>
-      <c r="N31" s="86">
+      <c r="N31" s="81">
         <v>8587.8559916459781</v>
       </c>
-      <c r="O31" s="86">
+      <c r="O31" s="81">
         <v>7280.8247477042542</v>
       </c>
-      <c r="P31" s="86">
+      <c r="P31" s="81">
         <v>20177.263779527562</v>
       </c>
-      <c r="Q31" s="88">
+      <c r="Q31" s="83">
         <v>7.5698048350311717</v>
       </c>
     </row>
@@ -4357,7 +4358,7 @@
       <c r="B32">
         <v>243</v>
       </c>
-      <c r="C32" s="85">
+      <c r="C32" s="80">
         <v>40056</v>
       </c>
       <c r="D32" t="s">
@@ -4366,40 +4367,40 @@
       <c r="E32">
         <v>22</v>
       </c>
-      <c r="F32" s="86">
+      <c r="F32" s="81">
         <v>11.625</v>
       </c>
-      <c r="G32" s="86">
+      <c r="G32" s="81">
         <v>0.125</v>
       </c>
-      <c r="H32" s="86">
+      <c r="H32" s="81">
         <v>3.5</v>
       </c>
-      <c r="I32" s="86">
+      <c r="I32" s="81">
         <v>4.5</v>
       </c>
-      <c r="J32" s="87">
+      <c r="J32" s="82">
         <v>20.91375</v>
       </c>
-      <c r="K32" s="87">
+      <c r="K32" s="82">
         <v>33.577500000000001</v>
       </c>
-      <c r="L32" s="87">
+      <c r="L32" s="82">
         <v>95.076363636363624</v>
       </c>
-      <c r="M32" s="86">
+      <c r="M32" s="81">
         <v>4884.9531391540659</v>
       </c>
-      <c r="N32" s="86">
+      <c r="N32" s="81">
         <v>7842.9030675964686</v>
       </c>
-      <c r="O32" s="86">
+      <c r="O32" s="81">
         <v>7859.5453680526143</v>
       </c>
-      <c r="P32" s="86">
+      <c r="P32" s="81">
         <v>20587.401574803149</v>
       </c>
-      <c r="Q32" s="88">
+      <c r="Q32" s="83">
         <v>7.9538721752169499</v>
       </c>
     </row>
@@ -4410,7 +4411,7 @@
       <c r="B33">
         <v>243</v>
       </c>
-      <c r="C33" s="85">
+      <c r="C33" s="80">
         <v>40056</v>
       </c>
       <c r="D33" t="s">
@@ -4419,40 +4420,40 @@
       <c r="E33">
         <v>18</v>
       </c>
-      <c r="F33" s="86">
+      <c r="F33" s="81">
         <v>11.125</v>
       </c>
-      <c r="G33" s="86">
+      <c r="G33" s="81">
         <v>0.25</v>
       </c>
-      <c r="H33" s="86">
+      <c r="H33" s="81">
         <v>3.625</v>
       </c>
-      <c r="I33" s="86">
+      <c r="I33" s="81">
         <v>4.75</v>
       </c>
-      <c r="J33" s="87">
+      <c r="J33" s="82">
         <v>20.2925</v>
       </c>
-      <c r="K33" s="87">
+      <c r="K33" s="82">
         <v>30.617500000000003</v>
       </c>
-      <c r="L33" s="87">
+      <c r="L33" s="82">
         <v>102.22777777777776</v>
       </c>
-      <c r="M33" s="86">
+      <c r="M33" s="81">
         <v>4320.991610569723</v>
       </c>
-      <c r="N33" s="86">
+      <c r="N33" s="81">
         <v>6519.5496186580513</v>
       </c>
-      <c r="O33" s="86">
+      <c r="O33" s="81">
         <v>7270.6792432131679</v>
       </c>
-      <c r="P33" s="86">
+      <c r="P33" s="81">
         <v>18111.220472440942</v>
       </c>
-      <c r="Q33" s="88">
+      <c r="Q33" s="83">
         <v>7.0396523189661417</v>
       </c>
     </row>
@@ -4503,10 +4504,9 @@
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>39974</v>
       </c>
-      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C6" s="5" t="s">
@@ -4516,23 +4516,21 @@
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7"/>
     </row>
     <row r="8" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>39974</v>
       </c>
-      <c r="F8" s="7"/>
       <c r="I8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <v>39981</v>
       </c>
     </row>
@@ -4544,41 +4542,37 @@
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
       <c r="L9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
     </row>
     <row r="11" spans="2:33" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
       <c r="R11" s="1" t="s">
         <v>52</v>
       </c>
@@ -4590,42 +4584,42 @@
       </c>
     </row>
     <row r="12" spans="2:33" ht="48.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="I12" s="23" t="s">
+      <c r="H12" s="13"/>
+      <c r="I12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="J12" s="23" t="s">
+      <c r="J12" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="L12" s="13" t="s">
+      <c r="L12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="15" t="s">
+      <c r="N12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="15" t="s">
+      <c r="O12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="P12" s="15" t="s">
+      <c r="P12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="R12" s="1" t="s">
@@ -4637,89 +4631,89 @@
       <c r="U12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="V12" s="84" t="s">
+      <c r="V12" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="W12" s="84" t="s">
+      <c r="W12" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="X12" s="84" t="s">
+      <c r="X12" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="Y12" s="84" t="s">
+      <c r="Y12" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="Z12" s="84" t="s">
+      <c r="Z12" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AA12" s="84" t="s">
+      <c r="AA12" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AB12" s="84" t="s">
+      <c r="AB12" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="AC12" s="84" t="s">
+      <c r="AC12" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="AD12" s="84" t="s">
+      <c r="AD12" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="AE12" s="84" t="s">
+      <c r="AE12" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="AF12" s="84" t="s">
+      <c r="AF12" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="AG12" s="84" t="s">
+      <c r="AG12" s="79" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:33" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>42</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25">
+      <c r="D13" s="25"/>
+      <c r="E13" s="24">
         <v>30</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28">
+      <c r="F13" s="26"/>
+      <c r="G13" s="27">
         <v>4794.3</v>
       </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="31">
+      <c r="H13" s="28"/>
+      <c r="I13" s="30">
         <v>379.36</v>
       </c>
-      <c r="J13" s="32">
+      <c r="J13" s="31">
         <v>62.79</v>
       </c>
-      <c r="K13" s="37">
+      <c r="K13" s="36">
         <f>I13-J13</f>
         <v>316.57</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="39">
         <v>25.6</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="33">
         <v>31.48</v>
       </c>
-      <c r="N13" s="34">
+      <c r="N13" s="33">
         <v>6.38</v>
       </c>
-      <c r="O13" s="34">
+      <c r="O13" s="33">
         <v>8.39</v>
       </c>
-      <c r="P13" s="34">
+      <c r="P13" s="33">
         <v>0.38</v>
       </c>
       <c r="R13" s="1">
         <f>G13/M13</f>
         <v>152.29669631512073</v>
       </c>
-      <c r="S13" s="76">
+      <c r="S13" s="75">
         <f>(K13-K13*O13/SUM(L13:P13)+SUM(L13:N13,P13))/(200*102)*100*100*10000/1000</f>
         <v>1684.5013070990547</v>
       </c>
@@ -4778,51 +4772,51 @@
       </c>
     </row>
     <row r="14" spans="2:33" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>43</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25">
+      <c r="D14" s="25"/>
+      <c r="E14" s="24">
         <v>25</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28">
+      <c r="F14" s="26"/>
+      <c r="G14" s="27">
         <v>5114.8500000000004</v>
       </c>
-      <c r="H14" s="29"/>
-      <c r="I14" s="33">
+      <c r="H14" s="28"/>
+      <c r="I14" s="32">
         <v>373.39</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="33">
         <v>64.540000000000006</v>
       </c>
-      <c r="K14" s="38">
+      <c r="K14" s="37">
         <f t="shared" ref="K14:K20" si="0">I14-J14</f>
         <v>308.84999999999997</v>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="39">
         <v>26.07</v>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="33">
         <v>32.58</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="33">
         <v>7.24</v>
       </c>
-      <c r="O14" s="34">
+      <c r="O14" s="33">
         <v>9.0299999999999994</v>
       </c>
-      <c r="P14" s="34">
+      <c r="P14" s="33">
         <v>0.26</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" ref="R14:R20" si="1">G14/M14</f>
         <v>156.99355432780848</v>
       </c>
-      <c r="S14" s="76">
+      <c r="S14" s="75">
         <f t="shared" ref="S14:S20" si="2">(K14-K14*O14/SUM(L14:P14)+SUM(L14:N14,P14))/(200*102)*100*100*10000/1000</f>
         <v>1656.3896648044692</v>
       </c>
@@ -4881,51 +4875,51 @@
       </c>
     </row>
     <row r="15" spans="2:33" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>45</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25">
+      <c r="D15" s="25"/>
+      <c r="E15" s="24">
         <v>28</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28">
+      <c r="F15" s="26"/>
+      <c r="G15" s="27">
         <v>4796.8999999999996</v>
       </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="33">
+      <c r="H15" s="28"/>
+      <c r="I15" s="32">
         <v>359.51</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="33">
         <v>65.23</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="37">
         <f t="shared" si="0"/>
         <v>294.27999999999997</v>
       </c>
-      <c r="L15" s="40">
+      <c r="L15" s="39">
         <v>24.53</v>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="33">
         <v>30.94</v>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="33">
         <v>6.54</v>
       </c>
-      <c r="O15" s="34">
+      <c r="O15" s="33">
         <v>8.24</v>
       </c>
-      <c r="P15" s="34">
+      <c r="P15" s="33">
         <v>0.26</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" si="1"/>
         <v>155.03878474466708</v>
       </c>
-      <c r="S15" s="76">
+      <c r="S15" s="75">
         <f t="shared" si="2"/>
         <v>1579.2137188161323</v>
       </c>
@@ -4984,47 +4978,47 @@
       </c>
     </row>
     <row r="16" spans="2:33" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>45</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25">
+      <c r="D16" s="25"/>
+      <c r="E16" s="24">
         <v>23</v>
       </c>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28">
+      <c r="F16" s="26"/>
+      <c r="G16" s="27">
         <v>5293.23</v>
       </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="33">
+      <c r="H16" s="28"/>
+      <c r="I16" s="32">
         <v>398.18</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="33">
         <v>63.06</v>
       </c>
-      <c r="K16" s="38">
+      <c r="K16" s="37">
         <f t="shared" si="0"/>
         <v>335.12</v>
       </c>
-      <c r="L16" s="40">
+      <c r="L16" s="39">
         <v>25.99</v>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="33">
         <v>3.47</v>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="33">
         <v>7.3</v>
       </c>
-      <c r="O16" s="34">
+      <c r="O16" s="33">
         <v>8.17</v>
       </c>
-      <c r="P16" s="34">
+      <c r="P16" s="33">
         <v>0.41</v>
       </c>
-      <c r="S16" s="76"/>
+      <c r="S16" s="75"/>
       <c r="U16" s="1">
         <f t="shared" si="4"/>
         <v>45</v>
@@ -5076,51 +5070,51 @@
       </c>
     </row>
     <row r="17" spans="2:33" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>40</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25">
+      <c r="D17" s="25"/>
+      <c r="E17" s="24">
         <v>22</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28">
+      <c r="F17" s="26"/>
+      <c r="G17" s="27">
         <v>4809.38</v>
       </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="33">
+      <c r="H17" s="28"/>
+      <c r="I17" s="32">
         <v>332.07</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J17" s="33">
         <v>62.61</v>
       </c>
-      <c r="K17" s="38">
+      <c r="K17" s="37">
         <f t="shared" si="0"/>
         <v>269.45999999999998</v>
       </c>
-      <c r="L17" s="40">
+      <c r="L17" s="39">
         <v>23.09</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="33">
         <v>32.090000000000003</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="33">
         <v>6.8</v>
       </c>
-      <c r="O17" s="34">
+      <c r="O17" s="33">
         <v>8.0500000000000007</v>
       </c>
-      <c r="P17" s="34">
+      <c r="P17" s="33">
         <v>0.24</v>
       </c>
       <c r="R17" s="1">
         <f t="shared" si="1"/>
         <v>149.87161109379869</v>
       </c>
-      <c r="S17" s="76">
+      <c r="S17" s="75">
         <f t="shared" si="2"/>
         <v>1474.5645367866796</v>
       </c>
@@ -5179,51 +5173,51 @@
       </c>
     </row>
     <row r="18" spans="2:33" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>40</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="25">
+      <c r="D18" s="25"/>
+      <c r="E18" s="24">
         <v>27</v>
       </c>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28">
+      <c r="F18" s="26"/>
+      <c r="G18" s="27">
         <v>5282.15</v>
       </c>
-      <c r="H18" s="29"/>
-      <c r="I18" s="33">
+      <c r="H18" s="28"/>
+      <c r="I18" s="32">
         <v>367.8</v>
       </c>
-      <c r="J18" s="34">
+      <c r="J18" s="33">
         <v>63.1</v>
       </c>
-      <c r="K18" s="38">
+      <c r="K18" s="37">
         <f t="shared" si="0"/>
         <v>304.7</v>
       </c>
-      <c r="L18" s="40">
+      <c r="L18" s="39">
         <v>26.03</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="33">
         <v>35.28</v>
       </c>
-      <c r="N18" s="34">
+      <c r="N18" s="33">
         <v>7.25</v>
       </c>
-      <c r="O18" s="34">
+      <c r="O18" s="33">
         <v>8.68</v>
       </c>
-      <c r="P18" s="34">
+      <c r="P18" s="33">
         <v>0.46</v>
       </c>
       <c r="R18" s="1">
         <f t="shared" si="1"/>
         <v>149.72080498866211</v>
       </c>
-      <c r="S18" s="76">
+      <c r="S18" s="75">
         <f t="shared" si="2"/>
         <v>1665.1051051051052</v>
       </c>
@@ -5282,44 +5276,44 @@
       </c>
     </row>
     <row r="19" spans="2:33" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>36</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="25">
+      <c r="D19" s="25"/>
+      <c r="E19" s="24">
         <v>28</v>
       </c>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28">
+      <c r="F19" s="26"/>
+      <c r="G19" s="27">
         <v>5536.15</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="33">
+      <c r="H19" s="28"/>
+      <c r="I19" s="32">
         <v>340.45</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="33">
         <v>62.86</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19" s="37">
         <f t="shared" si="0"/>
         <v>277.58999999999997</v>
       </c>
-      <c r="L19" s="40">
+      <c r="L19" s="39">
         <v>32.520000000000003</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="33">
         <v>39.31</v>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="33">
         <v>7.91</v>
       </c>
-      <c r="O19" s="34">
+      <c r="O19" s="33">
         <v>10.32</v>
       </c>
-      <c r="P19" s="34">
+      <c r="P19" s="33">
         <v>0.61</v>
       </c>
       <c r="Q19" s="2"/>
@@ -5327,7 +5321,7 @@
         <f t="shared" si="1"/>
         <v>140.83312134316967</v>
       </c>
-      <c r="S19" s="76">
+      <c r="S19" s="75">
         <f t="shared" si="2"/>
         <v>1599.7298434097361</v>
       </c>
@@ -5386,51 +5380,51 @@
       </c>
     </row>
     <row r="20" spans="2:33" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>34</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25">
+      <c r="D20" s="25"/>
+      <c r="E20" s="24">
         <v>34</v>
       </c>
-      <c r="F20" s="27"/>
-      <c r="G20" s="28">
+      <c r="F20" s="26"/>
+      <c r="G20" s="27">
         <v>6494.6</v>
       </c>
-      <c r="H20" s="29"/>
-      <c r="I20" s="35">
+      <c r="H20" s="28"/>
+      <c r="I20" s="34">
         <v>368.59</v>
       </c>
-      <c r="J20" s="36">
+      <c r="J20" s="35">
         <v>62.73</v>
       </c>
-      <c r="K20" s="39">
+      <c r="K20" s="38">
         <f t="shared" si="0"/>
         <v>305.85999999999996</v>
       </c>
-      <c r="L20" s="40">
+      <c r="L20" s="39">
         <v>34</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="33">
         <v>41.71</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="33">
         <v>8.2200000000000006</v>
       </c>
-      <c r="O20" s="34">
+      <c r="O20" s="33">
         <v>10.210000000000001</v>
       </c>
-      <c r="P20" s="34">
+      <c r="P20" s="33">
         <v>0.93</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" si="1"/>
         <v>155.70846319827379</v>
       </c>
-      <c r="S20" s="76">
+      <c r="S20" s="75">
         <f t="shared" si="2"/>
         <v>1754.2759927153779</v>
       </c>
@@ -5710,11 +5704,11 @@
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>40001</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5726,26 +5720,23 @@
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
     </row>
     <row r="8" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C8" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="7"/>
+      <c r="F8" s="40"/>
       <c r="J8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="8">
         <v>40008</v>
       </c>
-      <c r="L8" s="41"/>
+      <c r="L8" s="40"/>
     </row>
     <row r="9" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C9" s="5" t="s">
@@ -5755,25 +5746,19 @@
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
       <c r="K9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
       <c r="R10" s="1" t="s">
         <v>52</v>
       </c>
@@ -5785,178 +5770,178 @@
       </c>
     </row>
     <row r="11" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="16"/>
     </row>
     <row r="12" spans="2:35" ht="48.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="23" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="24" t="s">
+      <c r="L12" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="N12" s="13" t="s">
+      <c r="N12" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="15" t="s">
+      <c r="O12" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="P12" s="42" t="s">
+      <c r="P12" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42" t="s">
+      <c r="Q12" s="41"/>
+      <c r="R12" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="S12" s="42" t="s">
+      <c r="S12" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="15" t="s">
+      <c r="T12" s="41"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="14" t="s">
         <v>12</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="X12" s="84" t="s">
+      <c r="X12" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="Y12" s="84" t="s">
+      <c r="Y12" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="Z12" s="84" t="s">
+      <c r="Z12" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AA12" s="84" t="s">
+      <c r="AA12" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AB12" s="84" t="s">
+      <c r="AB12" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AC12" s="84" t="s">
+      <c r="AC12" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AD12" s="84" t="s">
+      <c r="AD12" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="AE12" s="84" t="s">
+      <c r="AE12" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="AF12" s="84" t="s">
+      <c r="AF12" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="AG12" s="84" t="s">
+      <c r="AG12" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="AH12" s="84" t="s">
+      <c r="AH12" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="AI12" s="84" t="s">
+      <c r="AI12" s="79" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="2:35" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="22">
+      <c r="B13" s="21">
         <v>2</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>21</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25">
+      <c r="D13" s="25"/>
+      <c r="E13" s="24">
         <v>95</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <v>3</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <v>21</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <v>16931.650000000001</v>
       </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="50">
+      <c r="I13" s="28"/>
+      <c r="J13" s="49">
         <v>425.9</v>
       </c>
-      <c r="K13" s="51">
+      <c r="K13" s="50">
         <v>61.65</v>
       </c>
-      <c r="L13" s="52">
+      <c r="L13" s="51">
         <f>J13-K13</f>
         <v>364.25</v>
       </c>
-      <c r="M13" s="49">
+      <c r="M13" s="48">
         <v>87.62</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="29">
         <v>82.85</v>
       </c>
-      <c r="O13" s="30">
+      <c r="O13" s="29">
         <v>19.46</v>
       </c>
-      <c r="P13" s="30">
+      <c r="P13" s="29">
         <v>17.57</v>
       </c>
-      <c r="Q13" s="77"/>
-      <c r="R13" s="77">
+      <c r="Q13" s="76"/>
+      <c r="R13" s="76">
         <f>H13/N13</f>
         <v>204.36511768255886</v>
       </c>
-      <c r="S13" s="77">
+      <c r="S13" s="76">
         <f>SUM(L13:P13)/(100*102)*100*100*10000/1000</f>
         <v>5605.3921568627457</v>
       </c>
-      <c r="T13" s="77">
+      <c r="T13" s="76">
         <f>H13*SUM(L13:P13)/SUM(M13:P13)/(100*102)</f>
         <v>4.5739054512166319</v>
       </c>
-      <c r="U13" s="77"/>
+      <c r="U13" s="76"/>
       <c r="V13" s="3" t="s">
         <v>33</v>
       </c>
@@ -6013,62 +5998,62 @@
       </c>
     </row>
     <row r="14" spans="2:35" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>4</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>4</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25">
+      <c r="D14" s="25"/>
+      <c r="E14" s="24">
         <v>123</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <v>4</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <v>15</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="24">
         <v>21179.64</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="53">
+      <c r="I14" s="28"/>
+      <c r="J14" s="52">
         <v>373.18</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="29">
         <v>61.96</v>
       </c>
-      <c r="L14" s="54">
+      <c r="L14" s="53">
         <f t="shared" ref="L14:L20" si="0">J14-K14</f>
         <v>311.22000000000003</v>
       </c>
-      <c r="M14" s="49">
+      <c r="M14" s="48">
         <v>112.56</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="29">
         <v>106.62</v>
       </c>
-      <c r="O14" s="30">
+      <c r="O14" s="29">
         <v>24.92</v>
       </c>
-      <c r="P14" s="30">
+      <c r="P14" s="29">
         <v>16.09</v>
       </c>
-      <c r="Q14" s="77"/>
-      <c r="R14" s="77">
+      <c r="Q14" s="76"/>
+      <c r="R14" s="76">
         <f t="shared" ref="R14:R20" si="1">H14/N14</f>
         <v>198.64603263927967</v>
       </c>
-      <c r="S14" s="77">
+      <c r="S14" s="76">
         <f t="shared" ref="S14:S20" si="2">SUM(L14:P14)/(100*102)*100*100*10000/1000</f>
         <v>5602.0588235294126</v>
       </c>
-      <c r="T14" s="77">
+      <c r="T14" s="76">
         <f t="shared" ref="T14:T20" si="3">H14*SUM(L14:P14)/SUM(M14:P14)/(100*102)</f>
         <v>4.5601133456772542</v>
       </c>
-      <c r="U14" s="77"/>
+      <c r="U14" s="76"/>
       <c r="V14" s="3" t="s">
         <v>33</v>
       </c>
@@ -6125,62 +6110,62 @@
       </c>
     </row>
     <row r="15" spans="2:35" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>6</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>18</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25">
+      <c r="D15" s="25"/>
+      <c r="E15" s="24">
         <v>103</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <v>5</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <v>24</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <v>18894.150000000001</v>
       </c>
-      <c r="I15" s="29"/>
-      <c r="J15" s="53">
+      <c r="I15" s="28"/>
+      <c r="J15" s="52">
         <v>311.8</v>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="29">
         <v>62.53</v>
       </c>
-      <c r="L15" s="54">
+      <c r="L15" s="53">
         <f t="shared" si="0"/>
         <v>249.27</v>
       </c>
-      <c r="M15" s="49">
+      <c r="M15" s="48">
         <v>98.66</v>
       </c>
-      <c r="N15" s="30">
+      <c r="N15" s="29">
         <v>96.25</v>
       </c>
-      <c r="O15" s="30">
+      <c r="O15" s="29">
         <v>20.14</v>
       </c>
-      <c r="P15" s="30">
+      <c r="P15" s="29">
         <v>20.78</v>
       </c>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="77">
+      <c r="Q15" s="76"/>
+      <c r="R15" s="76">
         <f t="shared" si="1"/>
         <v>196.30285714285716</v>
       </c>
-      <c r="S15" s="77">
+      <c r="S15" s="76">
         <f t="shared" si="2"/>
         <v>4755.8823529411757</v>
       </c>
-      <c r="T15" s="77">
+      <c r="T15" s="76">
         <f t="shared" si="3"/>
         <v>3.8103021057042588</v>
       </c>
-      <c r="U15" s="77"/>
+      <c r="U15" s="76"/>
       <c r="V15" s="3" t="s">
         <v>33</v>
       </c>
@@ -6237,62 +6222,62 @@
       </c>
     </row>
     <row r="16" spans="2:35" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22">
+      <c r="B16" s="21">
         <v>8</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>19</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25">
+      <c r="D16" s="25"/>
+      <c r="E16" s="24">
         <v>127</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <v>6</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <v>14</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <v>19359.82</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="53">
+      <c r="I16" s="28"/>
+      <c r="J16" s="52">
         <v>416.07</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="29">
         <v>62.58</v>
       </c>
-      <c r="L16" s="54">
+      <c r="L16" s="53">
         <f t="shared" si="0"/>
         <v>353.49</v>
       </c>
-      <c r="M16" s="49">
+      <c r="M16" s="48">
         <v>107.55</v>
       </c>
-      <c r="N16" s="30">
+      <c r="N16" s="29">
         <v>99.54</v>
       </c>
-      <c r="O16" s="30">
+      <c r="O16" s="29">
         <v>22.77</v>
       </c>
-      <c r="P16" s="30">
+      <c r="P16" s="29">
         <v>18.71</v>
       </c>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="77">
+      <c r="Q16" s="76"/>
+      <c r="R16" s="76">
         <f t="shared" si="1"/>
         <v>194.4928671890697</v>
       </c>
-      <c r="S16" s="77">
+      <c r="S16" s="76">
         <f t="shared" si="2"/>
         <v>5902.5490196078435</v>
       </c>
-      <c r="T16" s="77">
+      <c r="T16" s="76">
         <f t="shared" si="3"/>
         <v>4.5971873742118641</v>
       </c>
-      <c r="U16" s="77"/>
+      <c r="U16" s="76"/>
       <c r="V16" s="3" t="s">
         <v>33</v>
       </c>
@@ -6349,62 +6334,62 @@
       </c>
     </row>
     <row r="17" spans="2:35" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>9</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>23</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25">
+      <c r="D17" s="25"/>
+      <c r="E17" s="24">
         <v>84</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>3</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>12</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>13540.34</v>
       </c>
-      <c r="I17" s="29"/>
-      <c r="J17" s="53">
+      <c r="I17" s="28"/>
+      <c r="J17" s="52">
         <v>454.75</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="29">
         <v>62.63</v>
       </c>
-      <c r="L17" s="54">
+      <c r="L17" s="53">
         <f t="shared" si="0"/>
         <v>392.12</v>
       </c>
-      <c r="M17" s="49">
+      <c r="M17" s="48">
         <v>73.099999999999994</v>
       </c>
-      <c r="N17" s="30">
+      <c r="N17" s="29">
         <v>78.33</v>
       </c>
-      <c r="O17" s="30">
+      <c r="O17" s="29">
         <v>16.71</v>
       </c>
-      <c r="P17" s="30">
+      <c r="P17" s="29">
         <v>13.48</v>
       </c>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77">
+      <c r="Q17" s="76"/>
+      <c r="R17" s="76">
         <f t="shared" si="1"/>
         <v>172.86276011745181</v>
       </c>
-      <c r="S17" s="77">
+      <c r="S17" s="76">
         <f t="shared" si="2"/>
         <v>5624.9019607843147</v>
       </c>
-      <c r="T17" s="77">
+      <c r="T17" s="76">
         <f t="shared" si="3"/>
         <v>4.193540635155065</v>
       </c>
-      <c r="U17" s="77"/>
+      <c r="U17" s="76"/>
       <c r="V17" s="3" t="s">
         <v>34</v>
       </c>
@@ -6461,62 +6446,62 @@
       </c>
     </row>
     <row r="18" spans="2:35" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="22">
+      <c r="B18" s="21">
         <v>11</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>24</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="25">
+      <c r="D18" s="25"/>
+      <c r="E18" s="24">
         <v>78</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="24">
         <v>2</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="24">
         <v>19</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="24">
         <v>15163.33</v>
       </c>
-      <c r="I18" s="29"/>
-      <c r="J18" s="53">
+      <c r="I18" s="28"/>
+      <c r="J18" s="52">
         <v>486.18</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="29">
         <v>63.39</v>
       </c>
-      <c r="L18" s="54">
+      <c r="L18" s="53">
         <f t="shared" si="0"/>
         <v>422.79</v>
       </c>
-      <c r="M18" s="49">
+      <c r="M18" s="48">
         <v>81.39</v>
       </c>
-      <c r="N18" s="30">
+      <c r="N18" s="29">
         <v>80.58</v>
       </c>
-      <c r="O18" s="30">
+      <c r="O18" s="29">
         <v>18.8</v>
       </c>
-      <c r="P18" s="30">
+      <c r="P18" s="29">
         <v>12.42</v>
       </c>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="77">
+      <c r="Q18" s="76"/>
+      <c r="R18" s="76">
         <f t="shared" si="1"/>
         <v>188.17733929014645</v>
       </c>
-      <c r="S18" s="77">
+      <c r="S18" s="76">
         <f t="shared" si="2"/>
         <v>6039.0196078431354</v>
       </c>
-      <c r="T18" s="77">
+      <c r="T18" s="76">
         <f t="shared" si="3"/>
         <v>4.7399786319269142</v>
       </c>
-      <c r="U18" s="77"/>
+      <c r="U18" s="76"/>
       <c r="V18" s="3" t="s">
         <v>34</v>
       </c>
@@ -6573,62 +6558,62 @@
       </c>
     </row>
     <row r="19" spans="2:35" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="22">
+      <c r="B19" s="21">
         <v>14</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>19</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="25">
+      <c r="D19" s="25"/>
+      <c r="E19" s="24">
         <v>128</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <v>7</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="24">
         <v>31</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="24">
         <v>19011.169999999998</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="53">
+      <c r="I19" s="28"/>
+      <c r="J19" s="52">
         <v>439.44</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="29">
         <v>61.29</v>
       </c>
-      <c r="L19" s="54">
+      <c r="L19" s="53">
         <f t="shared" si="0"/>
         <v>378.15</v>
       </c>
-      <c r="M19" s="49">
+      <c r="M19" s="48">
         <v>121.78</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="29">
         <v>116.39</v>
       </c>
-      <c r="O19" s="30">
+      <c r="O19" s="29">
         <v>25.78</v>
       </c>
-      <c r="P19" s="30">
+      <c r="P19" s="29">
         <v>33.03</v>
       </c>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="77">
+      <c r="Q19" s="76"/>
+      <c r="R19" s="76">
         <f t="shared" si="1"/>
         <v>163.34023541541367</v>
       </c>
-      <c r="S19" s="77">
+      <c r="S19" s="76">
         <f t="shared" si="2"/>
         <v>6618.9215686274511</v>
       </c>
-      <c r="T19" s="77">
+      <c r="T19" s="76">
         <f t="shared" si="3"/>
         <v>4.2371015946475552</v>
       </c>
-      <c r="U19" s="77"/>
+      <c r="U19" s="76"/>
       <c r="V19" s="3" t="s">
         <v>34</v>
       </c>
@@ -6685,62 +6670,62 @@
       </c>
     </row>
     <row r="20" spans="2:35" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="22">
+      <c r="B20" s="21">
         <v>15</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>28</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25">
+      <c r="D20" s="25"/>
+      <c r="E20" s="24">
         <v>73</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <v>6</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="24">
         <v>22</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <v>14724.01</v>
       </c>
-      <c r="I20" s="29"/>
-      <c r="J20" s="55">
+      <c r="I20" s="28"/>
+      <c r="J20" s="54">
         <v>545.47</v>
       </c>
-      <c r="K20" s="56">
+      <c r="K20" s="55">
         <v>61.29</v>
       </c>
-      <c r="L20" s="57">
+      <c r="L20" s="56">
         <f t="shared" si="0"/>
         <v>484.18</v>
       </c>
-      <c r="M20" s="49">
+      <c r="M20" s="48">
         <v>75.06</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="29">
         <v>79.069999999999993</v>
       </c>
-      <c r="O20" s="30">
+      <c r="O20" s="29">
         <v>16.71</v>
       </c>
-      <c r="P20" s="30">
+      <c r="P20" s="29">
         <v>20.89</v>
       </c>
-      <c r="Q20" s="77"/>
-      <c r="R20" s="77">
+      <c r="Q20" s="76"/>
+      <c r="R20" s="76">
         <f t="shared" si="1"/>
         <v>186.21487289743268</v>
       </c>
-      <c r="S20" s="77">
+      <c r="S20" s="76">
         <f t="shared" si="2"/>
         <v>6626.568627450979</v>
       </c>
-      <c r="T20" s="77">
+      <c r="T20" s="76">
         <f t="shared" si="3"/>
         <v>5.0889095465641523</v>
       </c>
-      <c r="U20" s="77"/>
+      <c r="U20" s="76"/>
       <c r="V20" s="3" t="s">
         <v>34</v>
       </c>
@@ -6797,15 +6782,15 @@
       </c>
     </row>
     <row r="21" spans="2:35" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="R21" s="76">
+      <c r="R21" s="75">
         <f>AVERAGE(R13:R20)</f>
         <v>188.05026029677626</v>
       </c>
-      <c r="S21" s="76">
+      <c r="S21" s="75">
         <f>AVERAGE(S13:S20)</f>
         <v>5846.9117647058811</v>
       </c>
-      <c r="T21" s="76">
+      <c r="T21" s="75">
         <f>AVERAGE(T13:T20)</f>
         <v>4.4751298356379614</v>
       </c>
@@ -6935,101 +6920,91 @@
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B5" s="47"/>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>40035</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="7"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
     </row>
     <row r="8" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="47"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="7"/>
+      <c r="F8" s="40"/>
       <c r="K8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L8" s="9">
+      <c r="L8" s="8">
         <v>40045</v>
       </c>
-      <c r="M8" s="41"/>
+      <c r="M8" s="40"/>
     </row>
     <row r="9" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="46" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
       <c r="L9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
     </row>
     <row r="11" spans="1:37" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
       <c r="V11" s="1" t="s">
         <v>52</v>
       </c>
@@ -7041,60 +7016,60 @@
       </c>
     </row>
     <row r="12" spans="1:37" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="68" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="67" t="s">
         <v>43</v>
       </c>
-      <c r="K12" s="69" t="s">
+      <c r="K12" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="70" t="s">
+      <c r="L12" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="M12" s="68" t="s">
+      <c r="M12" s="67" t="s">
         <v>44</v>
       </c>
-      <c r="N12" s="69" t="s">
+      <c r="N12" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="O12" s="70" t="s">
+      <c r="O12" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="P12" s="68" t="s">
+      <c r="P12" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="Q12" s="69" t="s">
+      <c r="Q12" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="70" t="s">
+      <c r="R12" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="S12" s="72" t="s">
+      <c r="S12" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="T12" s="74" t="s">
+      <c r="T12" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="U12" s="14" t="s">
         <v>12</v>
       </c>
       <c r="V12" s="1" t="s">
@@ -7106,104 +7081,104 @@
       <c r="Y12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z12" s="84" t="s">
+      <c r="Z12" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="AA12" s="84" t="s">
+      <c r="AA12" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="AB12" s="84" t="s">
+      <c r="AB12" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AC12" s="84" t="s">
+      <c r="AC12" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AD12" s="84" t="s">
+      <c r="AD12" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AE12" s="84" t="s">
+      <c r="AE12" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AF12" s="84" t="s">
+      <c r="AF12" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="AG12" s="84" t="s">
+      <c r="AG12" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="AH12" s="84" t="s">
+      <c r="AH12" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="AI12" s="84" t="s">
+      <c r="AI12" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="AJ12" s="84" t="s">
+      <c r="AJ12" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="AK12" s="84" t="s">
+      <c r="AK12" s="79" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="42">
         <v>1</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>19</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25">
+      <c r="D13" s="25"/>
+      <c r="E13" s="24">
         <v>19</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <v>2</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <v>65</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <v>24720.560000000001</v>
       </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="59">
+      <c r="I13" s="28"/>
+      <c r="J13" s="58">
         <v>798.61</v>
       </c>
-      <c r="K13" s="60">
+      <c r="K13" s="59">
         <v>62.03</v>
       </c>
-      <c r="L13" s="61">
+      <c r="L13" s="60">
         <f>J13-K13</f>
         <v>736.58</v>
       </c>
-      <c r="M13" s="59">
+      <c r="M13" s="58">
         <v>197.1</v>
       </c>
-      <c r="N13" s="60">
+      <c r="N13" s="59">
         <v>22.56</v>
       </c>
-      <c r="O13" s="61">
+      <c r="O13" s="60">
         <f t="shared" ref="O13:O20" si="0">M13-N13</f>
         <v>174.54</v>
       </c>
-      <c r="P13" s="59">
+      <c r="P13" s="58">
         <v>190.83</v>
       </c>
-      <c r="Q13" s="60">
+      <c r="Q13" s="59">
         <v>48.52</v>
       </c>
-      <c r="R13" s="61">
+      <c r="R13" s="60">
         <f t="shared" ref="R13:R20" si="1">P13-Q13</f>
         <v>142.31</v>
       </c>
-      <c r="S13" s="71">
+      <c r="S13" s="70">
         <v>30.71</v>
       </c>
-      <c r="T13" s="73">
+      <c r="T13" s="72">
         <v>177.89</v>
       </c>
-      <c r="U13" s="16"/>
+      <c r="U13" s="15"/>
       <c r="V13" s="1">
         <f>H13/R13</f>
         <v>173.70922633687022</v>
@@ -7269,64 +7244,64 @@
       </c>
     </row>
     <row r="14" spans="1:37" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="82"/>
-      <c r="B14" s="43">
+      <c r="A14" s="85"/>
+      <c r="B14" s="42">
         <v>3</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>20</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25">
+      <c r="D14" s="25"/>
+      <c r="E14" s="24">
         <v>98</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <v>5</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <v>58</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="24">
         <v>28270.14</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="62">
+      <c r="I14" s="28"/>
+      <c r="J14" s="61">
         <v>921.7</v>
       </c>
-      <c r="K14" s="30">
+      <c r="K14" s="29">
         <v>62.49</v>
       </c>
-      <c r="L14" s="63">
+      <c r="L14" s="62">
         <f t="shared" ref="L14:L20" si="2">J14-K14</f>
         <v>859.21</v>
       </c>
-      <c r="M14" s="62">
+      <c r="M14" s="61">
         <v>233.82</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="29">
         <v>47.47</v>
       </c>
-      <c r="O14" s="63">
+      <c r="O14" s="62">
         <f t="shared" si="0"/>
         <v>186.35</v>
       </c>
-      <c r="P14" s="62">
+      <c r="P14" s="61">
         <v>210.17</v>
       </c>
-      <c r="Q14" s="30">
+      <c r="Q14" s="29">
         <v>46.88</v>
       </c>
-      <c r="R14" s="63">
+      <c r="R14" s="62">
         <f t="shared" si="1"/>
         <v>163.29</v>
       </c>
-      <c r="S14" s="67">
+      <c r="S14" s="66">
         <v>34.85</v>
       </c>
-      <c r="T14" s="58">
+      <c r="T14" s="57">
         <v>156.08000000000001</v>
       </c>
-      <c r="U14" s="16"/>
+      <c r="U14" s="15"/>
       <c r="V14" s="1">
         <f t="shared" ref="V14:V20" si="3">H14/R14</f>
         <v>173.1284218261988</v>
@@ -7392,64 +7367,64 @@
       </c>
     </row>
     <row r="15" spans="1:37" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82"/>
-      <c r="B15" s="43">
+      <c r="A15" s="85"/>
+      <c r="B15" s="42">
         <v>5</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>24</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25">
+      <c r="D15" s="25"/>
+      <c r="E15" s="24">
         <v>26</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <v>0</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <v>63</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <v>29226.52</v>
       </c>
-      <c r="I15" s="29"/>
-      <c r="J15" s="62">
+      <c r="I15" s="28"/>
+      <c r="J15" s="61">
         <v>1040.06</v>
       </c>
-      <c r="K15" s="30">
+      <c r="K15" s="29">
         <v>63.58</v>
       </c>
-      <c r="L15" s="63">
+      <c r="L15" s="62">
         <f t="shared" si="2"/>
         <v>976.4799999999999</v>
       </c>
-      <c r="M15" s="62">
+      <c r="M15" s="61">
         <v>243.27</v>
       </c>
-      <c r="N15" s="30">
+      <c r="N15" s="29">
         <v>47.58</v>
       </c>
-      <c r="O15" s="63">
+      <c r="O15" s="62">
         <f t="shared" si="0"/>
         <v>195.69</v>
       </c>
-      <c r="P15" s="62">
+      <c r="P15" s="61">
         <v>201.4</v>
       </c>
-      <c r="Q15" s="30">
+      <c r="Q15" s="29">
         <v>47.58</v>
       </c>
-      <c r="R15" s="63">
+      <c r="R15" s="62">
         <f t="shared" si="1"/>
         <v>153.82</v>
       </c>
-      <c r="S15" s="67">
+      <c r="S15" s="66">
         <v>34.1</v>
       </c>
-      <c r="T15" s="58">
+      <c r="T15" s="57">
         <v>209.28</v>
       </c>
-      <c r="U15" s="16"/>
+      <c r="U15" s="15"/>
       <c r="V15" s="1">
         <f t="shared" si="3"/>
         <v>190.00468079573528</v>
@@ -7515,64 +7490,64 @@
       </c>
     </row>
     <row r="16" spans="1:37" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="83"/>
-      <c r="B16" s="43">
+      <c r="A16" s="86"/>
+      <c r="B16" s="42">
         <v>7</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>21</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25">
+      <c r="D16" s="25"/>
+      <c r="E16" s="24">
         <v>64</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <v>0</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <v>53</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <v>29879.47</v>
       </c>
-      <c r="I16" s="29"/>
-      <c r="J16" s="62">
+      <c r="I16" s="28"/>
+      <c r="J16" s="61">
         <v>937.54</v>
       </c>
-      <c r="K16" s="30">
+      <c r="K16" s="29">
         <v>61.22</v>
       </c>
-      <c r="L16" s="63">
+      <c r="L16" s="62">
         <f t="shared" si="2"/>
         <v>876.31999999999994</v>
       </c>
-      <c r="M16" s="62">
+      <c r="M16" s="61">
         <v>240.98</v>
       </c>
-      <c r="N16" s="30">
+      <c r="N16" s="29">
         <v>22.79</v>
       </c>
-      <c r="O16" s="63">
+      <c r="O16" s="62">
         <f t="shared" si="0"/>
         <v>218.19</v>
       </c>
-      <c r="P16" s="62">
+      <c r="P16" s="61">
         <v>239.9</v>
       </c>
-      <c r="Q16" s="30">
+      <c r="Q16" s="29">
         <v>58.54</v>
       </c>
-      <c r="R16" s="63">
+      <c r="R16" s="62">
         <f t="shared" si="1"/>
         <v>181.36</v>
       </c>
-      <c r="S16" s="67">
+      <c r="S16" s="66">
         <v>40.42</v>
       </c>
-      <c r="T16" s="58">
+      <c r="T16" s="57">
         <v>183.55</v>
       </c>
-      <c r="U16" s="16"/>
+      <c r="U16" s="15"/>
       <c r="V16" s="1">
         <f t="shared" si="3"/>
         <v>164.75226069695631</v>
@@ -7638,66 +7613,66 @@
       </c>
     </row>
     <row r="17" spans="1:37" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>10</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>22</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25">
+      <c r="D17" s="25"/>
+      <c r="E17" s="24">
         <v>12</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>1</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>51</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>22925.64</v>
       </c>
-      <c r="I17" s="29"/>
-      <c r="J17" s="62">
+      <c r="I17" s="28"/>
+      <c r="J17" s="61">
         <v>1047.72</v>
       </c>
-      <c r="K17" s="30">
+      <c r="K17" s="29">
         <v>56.74</v>
       </c>
-      <c r="L17" s="63">
+      <c r="L17" s="62">
         <f t="shared" si="2"/>
         <v>990.98</v>
       </c>
-      <c r="M17" s="62">
+      <c r="M17" s="61">
         <v>184.84</v>
       </c>
-      <c r="N17" s="30">
+      <c r="N17" s="29">
         <v>22.44</v>
       </c>
-      <c r="O17" s="63">
+      <c r="O17" s="62">
         <f t="shared" si="0"/>
         <v>162.4</v>
       </c>
-      <c r="P17" s="62">
+      <c r="P17" s="61">
         <v>156.55000000000001</v>
       </c>
-      <c r="Q17" s="30">
+      <c r="Q17" s="29">
         <v>22.7</v>
       </c>
-      <c r="R17" s="63">
+      <c r="R17" s="62">
         <f t="shared" si="1"/>
         <v>133.85000000000002</v>
       </c>
-      <c r="S17" s="67">
+      <c r="S17" s="66">
         <v>30.53</v>
       </c>
-      <c r="T17" s="58">
+      <c r="T17" s="57">
         <v>167.47</v>
       </c>
-      <c r="U17" s="16"/>
+      <c r="U17" s="15"/>
       <c r="V17" s="1">
         <f t="shared" si="3"/>
         <v>171.27859544265965</v>
@@ -7763,64 +7738,64 @@
       </c>
     </row>
     <row r="18" spans="1:37" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="82"/>
-      <c r="B18" s="22">
+      <c r="A18" s="85"/>
+      <c r="B18" s="21">
         <v>12</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>26</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="25">
+      <c r="D18" s="25"/>
+      <c r="E18" s="24">
         <v>27</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="24">
         <v>0</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="24">
         <v>44</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="24">
         <v>24194.63</v>
       </c>
-      <c r="I18" s="29"/>
-      <c r="J18" s="62">
+      <c r="I18" s="28"/>
+      <c r="J18" s="61">
         <v>1203.45</v>
       </c>
-      <c r="K18" s="30">
+      <c r="K18" s="29">
         <v>56.49</v>
       </c>
-      <c r="L18" s="63">
+      <c r="L18" s="62">
         <f t="shared" si="2"/>
         <v>1146.96</v>
       </c>
-      <c r="M18" s="62">
+      <c r="M18" s="61">
         <v>252.16</v>
       </c>
-      <c r="N18" s="30">
+      <c r="N18" s="29">
         <v>46.13</v>
       </c>
-      <c r="O18" s="63">
+      <c r="O18" s="62">
         <f t="shared" si="0"/>
         <v>206.03</v>
       </c>
-      <c r="P18" s="62">
+      <c r="P18" s="61">
         <v>195.14</v>
       </c>
-      <c r="Q18" s="30">
+      <c r="Q18" s="29">
         <v>47.19</v>
       </c>
-      <c r="R18" s="63">
+      <c r="R18" s="62">
         <f t="shared" si="1"/>
         <v>147.94999999999999</v>
       </c>
-      <c r="S18" s="67">
+      <c r="S18" s="66">
         <v>32.79</v>
       </c>
-      <c r="T18" s="58">
+      <c r="T18" s="57">
         <v>181.59</v>
       </c>
-      <c r="U18" s="16"/>
+      <c r="U18" s="15"/>
       <c r="V18" s="1">
         <f t="shared" si="3"/>
         <v>163.53247718823928</v>
@@ -7886,64 +7861,64 @@
       </c>
     </row>
     <row r="19" spans="1:37" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="22">
+      <c r="A19" s="85"/>
+      <c r="B19" s="21">
         <v>13</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>20</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="25">
+      <c r="D19" s="25"/>
+      <c r="E19" s="24">
         <v>68</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <v>5</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="24">
         <v>61</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="24">
         <v>25615.23</v>
       </c>
-      <c r="I19" s="29"/>
-      <c r="J19" s="62">
+      <c r="I19" s="28"/>
+      <c r="J19" s="61">
         <v>1066.1400000000001</v>
       </c>
-      <c r="K19" s="30">
+      <c r="K19" s="29">
         <v>57.08</v>
       </c>
-      <c r="L19" s="63">
+      <c r="L19" s="62">
         <f t="shared" si="2"/>
         <v>1009.0600000000001</v>
       </c>
-      <c r="M19" s="62">
+      <c r="M19" s="61">
         <v>189.7</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="29">
         <v>22.69</v>
       </c>
-      <c r="O19" s="63">
+      <c r="O19" s="62">
         <f t="shared" si="0"/>
         <v>167.01</v>
       </c>
-      <c r="P19" s="62">
+      <c r="P19" s="61">
         <v>180.73</v>
       </c>
-      <c r="Q19" s="30">
+      <c r="Q19" s="29">
         <v>22.62</v>
       </c>
-      <c r="R19" s="63">
+      <c r="R19" s="62">
         <f t="shared" si="1"/>
         <v>158.10999999999999</v>
       </c>
-      <c r="S19" s="67">
+      <c r="S19" s="66">
         <v>30.52</v>
       </c>
-      <c r="T19" s="58">
+      <c r="T19" s="57">
         <v>190.54</v>
       </c>
-      <c r="U19" s="16"/>
+      <c r="U19" s="15"/>
       <c r="V19" s="1">
         <f t="shared" si="3"/>
         <v>162.00891784200874</v>
@@ -8009,64 +7984,64 @@
       </c>
     </row>
     <row r="20" spans="1:37" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="83"/>
-      <c r="B20" s="22">
+      <c r="A20" s="86"/>
+      <c r="B20" s="21">
         <v>16</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>24</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25">
+      <c r="D20" s="25"/>
+      <c r="E20" s="24">
         <v>15</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <v>1</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="24">
         <v>55</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <v>20131.18</v>
       </c>
-      <c r="I20" s="29"/>
-      <c r="J20" s="64">
+      <c r="I20" s="28"/>
+      <c r="J20" s="63">
         <v>992.52</v>
       </c>
-      <c r="K20" s="65">
+      <c r="K20" s="64">
         <v>56.67</v>
       </c>
-      <c r="L20" s="66">
+      <c r="L20" s="65">
         <f t="shared" si="2"/>
         <v>935.85</v>
       </c>
-      <c r="M20" s="64">
+      <c r="M20" s="63">
         <v>207.26</v>
       </c>
-      <c r="N20" s="65">
+      <c r="N20" s="64">
         <v>45.54</v>
       </c>
-      <c r="O20" s="66">
+      <c r="O20" s="65">
         <f t="shared" si="0"/>
         <v>161.72</v>
       </c>
-      <c r="P20" s="64">
+      <c r="P20" s="63">
         <v>188.5</v>
       </c>
-      <c r="Q20" s="65">
+      <c r="Q20" s="64">
         <v>64.8</v>
       </c>
-      <c r="R20" s="66">
+      <c r="R20" s="65">
         <f t="shared" si="1"/>
         <v>123.7</v>
       </c>
-      <c r="S20" s="67">
+      <c r="S20" s="66">
         <v>26.15</v>
       </c>
-      <c r="T20" s="58">
+      <c r="T20" s="57">
         <v>186.19</v>
       </c>
-      <c r="U20" s="16"/>
+      <c r="U20" s="15"/>
       <c r="V20" s="1">
         <f t="shared" si="3"/>
         <v>162.74195634599837</v>
@@ -8268,113 +8243,98 @@
       </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B5" s="47"/>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>40056</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
     </row>
     <row r="8" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="47"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="F8" s="40"/>
       <c r="L8" s="5" t="s">
         <v>5</v>
       </c>
       <c r="M8" s="5"/>
-      <c r="N8" s="9">
+      <c r="N8" s="8">
         <v>40064</v>
       </c>
-      <c r="O8" s="41"/>
-      <c r="P8" s="41"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
     </row>
     <row r="9" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="46" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
       <c r="N9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
-      <c r="U10" s="17"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
     </row>
     <row r="11" spans="1:38" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
-      <c r="U11" s="20"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
       <c r="W11" s="1" t="s">
         <v>52</v>
       </c>
@@ -8386,60 +8346,60 @@
       </c>
     </row>
     <row r="12" spans="1:38" ht="54" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="44" t="s">
+      <c r="J12" s="13"/>
+      <c r="K12" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="48" t="s">
+      <c r="L12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="M12" s="48" t="s">
+      <c r="M12" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="44" t="s">
+      <c r="N12" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="O12" s="48" t="s">
+      <c r="O12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="48" t="s">
+      <c r="P12" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="Q12" s="44" t="s">
+      <c r="Q12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="R12" s="48" t="s">
+      <c r="R12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="S12" s="48" t="s">
+      <c r="S12" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="T12" s="45" t="s">
+      <c r="T12" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="U12" s="46" t="s">
+      <c r="U12" s="45" t="s">
         <v>46</v>
       </c>
       <c r="W12" s="1" t="s">
@@ -8451,104 +8411,104 @@
       <c r="Z12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AA12" s="84" t="s">
+      <c r="AA12" s="79" t="s">
         <v>72</v>
       </c>
-      <c r="AB12" s="84" t="s">
+      <c r="AB12" s="79" t="s">
         <v>73</v>
       </c>
-      <c r="AC12" s="84" t="s">
+      <c r="AC12" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="AD12" s="84" t="s">
+      <c r="AD12" s="79" t="s">
         <v>75</v>
       </c>
-      <c r="AE12" s="84" t="s">
+      <c r="AE12" s="79" t="s">
         <v>76</v>
       </c>
-      <c r="AF12" s="84" t="s">
+      <c r="AF12" s="79" t="s">
         <v>77</v>
       </c>
-      <c r="AG12" s="84" t="s">
+      <c r="AG12" s="79" t="s">
         <v>78</v>
       </c>
-      <c r="AH12" s="84" t="s">
+      <c r="AH12" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="AI12" s="84" t="s">
+      <c r="AI12" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="AJ12" s="84" t="s">
+      <c r="AJ12" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="AK12" s="84" t="s">
+      <c r="AK12" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="AL12" s="84" t="s">
+      <c r="AL12" s="79" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:38" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="81" t="s">
+      <c r="A13" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="21">
         <v>2</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="24">
         <v>22</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25">
+      <c r="D13" s="25"/>
+      <c r="E13" s="24">
         <v>45</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="24">
         <v>2</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="24">
         <v>71</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="24">
         <v>17</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="24">
         <v>24435.81</v>
       </c>
-      <c r="J13" s="26"/>
-      <c r="K13" s="30">
+      <c r="J13" s="25"/>
+      <c r="K13" s="29">
         <v>1265.9000000000001</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <v>56.57</v>
       </c>
-      <c r="M13" s="30">
+      <c r="M13" s="29">
         <f>K13-L13</f>
         <v>1209.3300000000002</v>
       </c>
-      <c r="N13" s="30">
+      <c r="N13" s="29">
         <v>231.5</v>
       </c>
-      <c r="O13" s="30">
+      <c r="O13" s="29">
         <v>22.42</v>
       </c>
-      <c r="P13" s="30">
+      <c r="P13" s="29">
         <f>N13-O13</f>
         <v>209.07999999999998</v>
       </c>
-      <c r="Q13" s="30">
+      <c r="Q13" s="29">
         <v>158.72999999999999</v>
       </c>
-      <c r="R13" s="30">
+      <c r="R13" s="29">
         <v>23.28</v>
       </c>
-      <c r="S13" s="30">
+      <c r="S13" s="29">
         <f>Q13-R13</f>
         <v>135.44999999999999</v>
       </c>
-      <c r="T13" s="30">
+      <c r="T13" s="29">
         <v>30.99</v>
       </c>
-      <c r="U13" s="30">
+      <c r="U13" s="29">
         <v>289.94</v>
       </c>
       <c r="W13" s="1">
@@ -8617,64 +8577,64 @@
       </c>
     </row>
     <row r="14" spans="1:38" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="82"/>
-      <c r="B14" s="22">
+      <c r="A14" s="85"/>
+      <c r="B14" s="21">
         <v>4</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="24">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25">
+      <c r="D14" s="25"/>
+      <c r="E14" s="24">
         <v>50</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="24">
         <v>1</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <v>41</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="24">
         <v>29</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="24">
         <v>27565.52</v>
       </c>
-      <c r="J14" s="26"/>
-      <c r="K14" s="30">
+      <c r="J14" s="25"/>
+      <c r="K14" s="29">
         <v>1256.75</v>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="29">
         <v>57.11</v>
       </c>
-      <c r="M14" s="30">
+      <c r="M14" s="29">
         <f t="shared" ref="M14:M20" si="0">K14-L14</f>
         <v>1199.6400000000001</v>
       </c>
-      <c r="N14" s="30">
+      <c r="N14" s="29">
         <v>243.81</v>
       </c>
-      <c r="O14" s="30">
+      <c r="O14" s="29">
         <v>22.76</v>
       </c>
-      <c r="P14" s="30">
+      <c r="P14" s="29">
         <f t="shared" ref="P14:P20" si="1">N14-O14</f>
         <v>221.05</v>
       </c>
-      <c r="Q14" s="30">
+      <c r="Q14" s="29">
         <v>180.98</v>
       </c>
-      <c r="R14" s="30">
+      <c r="R14" s="29">
         <v>23.17</v>
       </c>
-      <c r="S14" s="30">
+      <c r="S14" s="29">
         <f t="shared" ref="S14:S20" si="2">Q14-R14</f>
         <v>157.81</v>
       </c>
-      <c r="T14" s="30">
+      <c r="T14" s="29">
         <v>35.29</v>
       </c>
-      <c r="U14" s="30">
+      <c r="U14" s="29">
         <v>316.8</v>
       </c>
       <c r="W14" s="1">
@@ -8690,117 +8650,117 @@
         <v>7.1378661474390697</v>
       </c>
       <c r="Z14" s="1">
-        <f t="shared" ref="Z14:Z20" si="6">C14</f>
+        <f t="shared" ref="Z14:Z19" si="6">C14</f>
         <v>18</v>
       </c>
       <c r="AA14">
-        <f t="shared" ref="AA14:AA20" si="7">E14/8</f>
+        <f t="shared" ref="AA14:AA19" si="7">E14/8</f>
         <v>6.25</v>
       </c>
       <c r="AB14">
-        <f t="shared" ref="AB14:AB20" si="8">F14/8</f>
+        <f t="shared" ref="AB14:AB19" si="8">F14/8</f>
         <v>0.125</v>
       </c>
       <c r="AC14">
-        <f t="shared" ref="AC14:AC20" si="9">G14/8</f>
+        <f t="shared" ref="AC14:AC19" si="9">G14/8</f>
         <v>5.125</v>
       </c>
       <c r="AD14">
-        <f t="shared" ref="AD14:AD20" si="10">H14/8</f>
+        <f t="shared" ref="AD14:AD19" si="10">H14/8</f>
         <v>3.625</v>
       </c>
       <c r="AE14">
-        <f t="shared" ref="AE14:AE20" si="11">S14/8</f>
+        <f t="shared" ref="AE14:AE19" si="11">S14/8</f>
         <v>19.72625</v>
       </c>
       <c r="AF14">
-        <f t="shared" ref="AF14:AF20" si="12">(P14+T14)/8</f>
+        <f t="shared" ref="AF14:AF19" si="12">(P14+T14)/8</f>
         <v>32.042500000000004</v>
       </c>
       <c r="AG14">
-        <f t="shared" ref="AG14:AG20" si="13">SUM(M14,P14,S14:U14)/C14</f>
+        <f t="shared" ref="AG14:AG19" si="13">SUM(M14,P14,S14:U14)/C14</f>
         <v>107.255</v>
       </c>
       <c r="AH14">
-        <f t="shared" ref="AH14:AH20" si="14">AK14*(S14/SUM(P14,S14:U14))</f>
+        <f t="shared" ref="AH14:AH19" si="14">AK14*(S14/SUM(P14,S14:U14))</f>
         <v>4102.4490281496464</v>
       </c>
       <c r="AI14">
-        <f t="shared" ref="AI14:AI20" si="15">AK14*(SUM(P14,T14)/SUM(P14,S14:U14))</f>
+        <f t="shared" ref="AI14:AI19" si="15">AK14*(SUM(P14,T14)/SUM(P14,S14:U14))</f>
         <v>6663.8475627392463</v>
       </c>
       <c r="AJ14">
-        <f t="shared" ref="AJ14:AJ20" si="16">AK14*(U14/SUM(P14,S14:U14))</f>
+        <f t="shared" ref="AJ14:AJ19" si="16">AK14*(U14/SUM(P14,S14:U14))</f>
         <v>8235.5734878512649</v>
       </c>
       <c r="AK14">
-        <f t="shared" ref="AK14:AK20" si="17">SUM(M14,P14,S14:U14)/1000/(1.016*1)*10000</f>
+        <f t="shared" ref="AK14:AK19" si="17">SUM(M14,P14,S14:U14)/1000/(1.016*1)*10000</f>
         <v>19001.870078740158</v>
       </c>
       <c r="AL14">
-        <f t="shared" ref="AL14:AL20" si="18">(I14*SUM(M14,P14,S14:U14)/SUM(P14,S14:U14)/(100*100)/(1.016*1))</f>
+        <f t="shared" ref="AL14:AL19" si="18">(I14*SUM(M14,P14,S14:U14)/SUM(P14,S14:U14)/(100*100)/(1.016*1))</f>
         <v>7.1659679826652072</v>
       </c>
     </row>
     <row r="15" spans="1:38" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82"/>
-      <c r="B15" s="22">
+      <c r="A15" s="85"/>
+      <c r="B15" s="21">
         <v>6</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="24">
         <v>21</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25">
+      <c r="D15" s="25"/>
+      <c r="E15" s="24">
         <v>75</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="24">
         <v>3</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="24">
         <v>58</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="24">
         <v>22</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="24">
         <v>27929.27</v>
       </c>
-      <c r="J15" s="26"/>
-      <c r="K15" s="30">
+      <c r="J15" s="25"/>
+      <c r="K15" s="29">
         <v>1139.06</v>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="29">
         <v>55.79</v>
       </c>
-      <c r="M15" s="30">
+      <c r="M15" s="29">
         <f t="shared" si="0"/>
         <v>1083.27</v>
       </c>
-      <c r="N15" s="30">
+      <c r="N15" s="29">
         <v>273.19</v>
       </c>
-      <c r="O15" s="30">
+      <c r="O15" s="29">
         <v>22.41</v>
       </c>
-      <c r="P15" s="30">
+      <c r="P15" s="29">
         <f t="shared" si="1"/>
         <v>250.78</v>
       </c>
-      <c r="Q15" s="30">
+      <c r="Q15" s="29">
         <v>174.98</v>
       </c>
-      <c r="R15" s="30">
+      <c r="R15" s="29">
         <v>23.17</v>
       </c>
-      <c r="S15" s="30">
+      <c r="S15" s="29">
         <f t="shared" si="2"/>
         <v>151.81</v>
       </c>
-      <c r="T15" s="30">
+      <c r="T15" s="29">
         <v>36.08</v>
       </c>
-      <c r="U15" s="30">
+      <c r="U15" s="29">
         <v>178.43</v>
       </c>
       <c r="W15" s="1">
@@ -8869,64 +8829,64 @@
       </c>
     </row>
     <row r="16" spans="1:38" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="83"/>
-      <c r="B16" s="22">
+      <c r="A16" s="86"/>
+      <c r="B16" s="21">
         <v>8</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="24">
         <v>19</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25">
+      <c r="D16" s="25"/>
+      <c r="E16" s="24">
         <v>48</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="24">
         <v>0</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="24">
         <v>44</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="24">
         <v>27</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="24">
         <v>25087.11</v>
       </c>
-      <c r="J16" s="26"/>
-      <c r="K16" s="30">
+      <c r="J16" s="25"/>
+      <c r="K16" s="29">
         <v>997.5</v>
       </c>
-      <c r="L16" s="30">
+      <c r="L16" s="29">
         <v>57.28</v>
       </c>
-      <c r="M16" s="30">
+      <c r="M16" s="29">
         <f t="shared" si="0"/>
         <v>940.22</v>
       </c>
-      <c r="N16" s="30">
+      <c r="N16" s="29">
         <v>237.54</v>
       </c>
-      <c r="O16" s="30">
+      <c r="O16" s="29">
         <v>22.43</v>
       </c>
-      <c r="P16" s="30">
+      <c r="P16" s="29">
         <f t="shared" si="1"/>
         <v>215.10999999999999</v>
       </c>
-      <c r="Q16" s="30">
+      <c r="Q16" s="29">
         <v>179.07</v>
       </c>
-      <c r="R16" s="30">
+      <c r="R16" s="29">
         <v>23.08</v>
       </c>
-      <c r="S16" s="30">
+      <c r="S16" s="29">
         <f t="shared" si="2"/>
         <v>155.99</v>
       </c>
-      <c r="T16" s="30">
+      <c r="T16" s="29">
         <v>32.520000000000003</v>
       </c>
-      <c r="U16" s="30">
+      <c r="U16" s="29">
         <v>278.18</v>
       </c>
       <c r="W16" s="1">
@@ -8995,66 +8955,66 @@
       </c>
     </row>
     <row r="17" spans="1:38" ht="40.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="81" t="s">
+      <c r="A17" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>9</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="24">
         <v>20</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25">
+      <c r="D17" s="25"/>
+      <c r="E17" s="24">
         <v>54</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="24">
         <v>1</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>88</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>23</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>28171.87</v>
       </c>
-      <c r="J17" s="26"/>
-      <c r="K17" s="30">
+      <c r="J17" s="25"/>
+      <c r="K17" s="29">
         <v>1220.1500000000001</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="29">
         <v>57.11</v>
       </c>
-      <c r="M17" s="30">
+      <c r="M17" s="29">
         <f t="shared" si="0"/>
         <v>1163.0400000000002</v>
       </c>
-      <c r="N17" s="30">
+      <c r="N17" s="29">
         <v>264.45</v>
       </c>
-      <c r="O17" s="30">
+      <c r="O17" s="29">
         <v>22.29</v>
       </c>
-      <c r="P17" s="30">
+      <c r="P17" s="29">
         <f t="shared" si="1"/>
         <v>242.16</v>
       </c>
-      <c r="Q17" s="30">
+      <c r="Q17" s="29">
         <v>185.99</v>
       </c>
-      <c r="R17" s="30">
+      <c r="R17" s="29">
         <v>23.11</v>
       </c>
-      <c r="S17" s="30">
+      <c r="S17" s="29">
         <f t="shared" si="2"/>
         <v>162.88</v>
       </c>
-      <c r="T17" s="30">
+      <c r="T17" s="29">
         <v>36.590000000000003</v>
       </c>
-      <c r="U17" s="30">
+      <c r="U17" s="29">
         <v>243.19</v>
       </c>
       <c r="W17" s="1">
@@ -9123,64 +9083,64 @@
       </c>
     </row>
     <row r="18" spans="1:38" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="82"/>
-      <c r="B18" s="22">
+      <c r="A18" s="85"/>
+      <c r="B18" s="21">
         <v>11</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="24">
         <v>21</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="25">
+      <c r="D18" s="25"/>
+      <c r="E18" s="24">
         <v>51</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="24">
         <v>1</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="24">
         <v>68</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="24">
         <v>29</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="24">
         <v>30475.41</v>
       </c>
-      <c r="J18" s="26"/>
-      <c r="K18" s="30">
+      <c r="J18" s="25"/>
+      <c r="K18" s="29">
         <v>1294.05</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="29">
         <v>56.36</v>
       </c>
-      <c r="M18" s="30">
+      <c r="M18" s="29">
         <f t="shared" si="0"/>
         <v>1237.69</v>
       </c>
-      <c r="N18" s="30">
+      <c r="N18" s="29">
         <v>324.2</v>
       </c>
-      <c r="O18" s="30">
+      <c r="O18" s="29">
         <v>22.62</v>
       </c>
-      <c r="P18" s="30">
+      <c r="P18" s="29">
         <f t="shared" si="1"/>
         <v>301.58</v>
       </c>
-      <c r="Q18" s="30">
+      <c r="Q18" s="29">
         <v>196.46</v>
       </c>
-      <c r="R18" s="30">
+      <c r="R18" s="29">
         <v>23</v>
       </c>
-      <c r="S18" s="30">
+      <c r="S18" s="29">
         <f t="shared" si="2"/>
         <v>173.46</v>
       </c>
-      <c r="T18" s="30">
+      <c r="T18" s="29">
         <v>44.16</v>
       </c>
-      <c r="U18" s="30">
+      <c r="U18" s="29">
         <v>293.12</v>
       </c>
       <c r="W18" s="1">
@@ -9249,64 +9209,64 @@
       </c>
     </row>
     <row r="19" spans="1:38" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="82"/>
-      <c r="B19" s="22">
+      <c r="A19" s="85"/>
+      <c r="B19" s="21">
         <v>14</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>22</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="25">
+      <c r="D19" s="25"/>
+      <c r="E19" s="24">
         <v>93</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="24">
         <v>1</v>
       </c>
-      <c r="G19" s="25">
+      <c r="G19" s="24">
         <v>28</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="24">
         <v>36</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="24">
         <v>27242.07</v>
       </c>
-      <c r="J19" s="26"/>
-      <c r="K19" s="30">
+      <c r="J19" s="25"/>
+      <c r="K19" s="29">
         <v>1443.25</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="29">
         <v>56.69</v>
       </c>
-      <c r="M19" s="30">
+      <c r="M19" s="29">
         <f t="shared" si="0"/>
         <v>1386.56</v>
       </c>
-      <c r="N19" s="30">
+      <c r="N19" s="29">
         <v>256.36</v>
       </c>
-      <c r="O19" s="30">
+      <c r="O19" s="29">
         <v>23.26</v>
       </c>
-      <c r="P19" s="30">
+      <c r="P19" s="29">
         <f t="shared" si="1"/>
         <v>233.10000000000002</v>
       </c>
-      <c r="Q19" s="30">
+      <c r="Q19" s="29">
         <v>190.51</v>
       </c>
-      <c r="R19" s="30">
+      <c r="R19" s="29">
         <v>23.2</v>
       </c>
-      <c r="S19" s="30">
+      <c r="S19" s="29">
         <f t="shared" si="2"/>
         <v>167.31</v>
       </c>
-      <c r="T19" s="30">
+      <c r="T19" s="29">
         <v>35.520000000000003</v>
       </c>
-      <c r="U19" s="30">
+      <c r="U19" s="29">
         <v>269.19</v>
       </c>
       <c r="V19" s="2"/>
@@ -9376,64 +9336,64 @@
       </c>
     </row>
     <row r="20" spans="1:38" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="83"/>
-      <c r="B20" s="22">
+      <c r="A20" s="86"/>
+      <c r="B20" s="21">
         <v>15</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="24">
         <v>18</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25">
+      <c r="D20" s="25"/>
+      <c r="E20" s="24">
         <v>89</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="24">
         <v>2</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="24">
         <v>29</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="24">
         <v>38</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="24">
         <v>26448.03</v>
       </c>
-      <c r="J20" s="26"/>
-      <c r="K20" s="30">
+      <c r="J20" s="25"/>
+      <c r="K20" s="29">
         <v>1216.8499999999999</v>
       </c>
-      <c r="L20" s="30">
+      <c r="L20" s="29">
         <v>57.19</v>
       </c>
-      <c r="M20" s="30">
+      <c r="M20" s="29">
         <f t="shared" si="0"/>
         <v>1159.6599999999999</v>
       </c>
-      <c r="N20" s="30">
+      <c r="N20" s="29">
         <v>232.33</v>
       </c>
-      <c r="O20" s="30">
+      <c r="O20" s="29">
         <v>23.23</v>
       </c>
-      <c r="P20" s="30">
+      <c r="P20" s="29">
         <f t="shared" si="1"/>
         <v>209.10000000000002</v>
       </c>
-      <c r="Q20" s="30">
+      <c r="Q20" s="29">
         <v>185.46</v>
       </c>
-      <c r="R20" s="30">
+      <c r="R20" s="29">
         <v>23.12</v>
       </c>
-      <c r="S20" s="30">
+      <c r="S20" s="29">
         <f t="shared" si="2"/>
         <v>162.34</v>
       </c>
-      <c r="T20" s="30">
+      <c r="T20" s="29">
         <v>35.840000000000003</v>
       </c>
-      <c r="U20" s="30">
+      <c r="U20" s="29">
         <v>273.16000000000003</v>
       </c>
       <c r="W20" s="1">
@@ -9640,326 +9600,311 @@
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B5" s="47"/>
-      <c r="C5" s="47" t="s">
+      <c r="B5" s="46"/>
+      <c r="C5" s="46" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="6"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="40"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B6" s="47"/>
-      <c r="C6" s="47" t="s">
+      <c r="B6" s="46"/>
+      <c r="C6" s="46" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B7" s="47"/>
-      <c r="C7" s="47"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="46"/>
     </row>
     <row r="8" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="47"/>
-      <c r="C8" s="47" t="s">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46" t="s">
         <v>6</v>
       </c>
       <c r="D8" s="6"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="40"/>
       <c r="M8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="9"/>
-      <c r="O8" s="41"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="40"/>
     </row>
     <row r="9" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="47"/>
-      <c r="C9" s="47" t="s">
+      <c r="B9" s="46"/>
+      <c r="C9" s="46" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
       <c r="N9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C10" s="5"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="L10" s="17"/>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17"/>
-      <c r="R10" s="17"/>
-      <c r="S10" s="17"/>
-      <c r="T10" s="17"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
     </row>
     <row r="11" spans="2:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="8"/>
-      <c r="E11" s="10" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="12"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="20"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="20"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
     </row>
     <row r="12" spans="2:21" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="44" t="s">
+      <c r="J12" s="12"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="48" t="s">
+      <c r="M12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="N12" s="44" t="s">
+      <c r="N12" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="O12" s="48" t="s">
+      <c r="O12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="P12" s="44" t="s">
+      <c r="P12" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="Q12" s="48" t="s">
+      <c r="Q12" s="47" t="s">
         <v>39</v>
       </c>
-      <c r="R12" s="45" t="s">
+      <c r="R12" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="S12" s="15" t="s">
+      <c r="S12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="T12" s="46" t="s">
+      <c r="T12" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="U12" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="22">
+      <c r="B13" s="21">
         <v>2</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="16"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="15"/>
     </row>
     <row r="14" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="22">
+      <c r="B14" s="21">
         <v>4</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="16"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="15"/>
     </row>
     <row r="15" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>6</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="30"/>
-      <c r="P15" s="30"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="16"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="15"/>
     </row>
     <row r="16" spans="2:21" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="22">
+      <c r="B16" s="21">
         <v>8</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="16"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="15"/>
     </row>
     <row r="17" spans="2:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="22">
+      <c r="B17" s="21">
         <v>9</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="26"/>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="16"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="15"/>
     </row>
     <row r="18" spans="2:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="22">
+      <c r="B18" s="21">
         <v>11</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="16"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="15"/>
     </row>
     <row r="19" spans="2:29" s="4" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="22">
+      <c r="B19" s="21">
         <v>14</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="30"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="30"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="16"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="15"/>
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
@@ -9970,28 +9915,28 @@
       <c r="AC19" s="3"/>
     </row>
     <row r="20" spans="2:29" ht="40.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="22">
+      <c r="B20" s="21">
         <v>15</v>
       </c>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="26"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="16"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="15"/>
     </row>
     <row r="21" spans="2:29" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="2:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -10071,11 +10016,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
       <c r="B2" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" t="s">
         <v>54</v>
       </c>
       <c r="D2" t="s">
@@ -10083,24 +10027,24 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="78" t="s">
+      <c r="A3" t="s">
         <v>62</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="78">
+      <c r="A4">
         <v>161</v>
       </c>
-      <c r="B4" s="78">
+      <c r="B4">
         <v>151.49471943021436</v>
       </c>
-      <c r="C4" s="78">
+      <c r="C4">
         <v>1630.5400241052223</v>
       </c>
       <c r="D4">
@@ -10108,13 +10052,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="78">
+      <c r="A5">
         <v>188</v>
       </c>
-      <c r="B5" s="78">
+      <c r="B5">
         <v>188.05026029677626</v>
       </c>
-      <c r="C5" s="78">
+      <c r="C5">
         <v>5846.9117647058811</v>
       </c>
       <c r="D5">
@@ -10122,13 +10066,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="78">
+      <c r="A6">
         <v>222</v>
       </c>
-      <c r="B6" s="78">
+      <c r="B6">
         <v>170.14456705933333</v>
       </c>
-      <c r="C6" s="78">
+      <c r="C6">
         <v>14608.357843137255</v>
       </c>
       <c r="D6">
@@ -10136,13 +10080,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="78">
+      <c r="A7">
         <v>243</v>
       </c>
-      <c r="B7" s="78">
+      <c r="B7">
         <v>171.78423960039615</v>
       </c>
-      <c r="C7" s="78">
+      <c r="C7">
         <v>18330.171568627447</v>
       </c>
       <c r="D7">
@@ -10150,10 +10094,10 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="78">
+      <c r="A8">
         <v>266</v>
       </c>
-      <c r="C8" s="78">
+      <c r="C8">
         <v>19500</v>
       </c>
     </row>
@@ -10169,10 +10113,10 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="80" t="s">
+      <c r="B11" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="79">
+      <c r="C11" s="77">
         <v>5136.25</v>
       </c>
       <c r="D11">
@@ -10180,10 +10124,10 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="79">
+      <c r="C12" s="77">
         <v>5113</v>
       </c>
       <c r="D12">
@@ -10191,10 +10135,10 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="78" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="79">
+      <c r="C13" s="77">
         <v>4252.25</v>
       </c>
       <c r="D13">
@@ -10202,10 +10146,10 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="78" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="79">
+      <c r="C14" s="77">
         <v>4684</v>
       </c>
       <c r="D14">
@@ -10213,7 +10157,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C15" s="79"/>
+      <c r="C15" s="77"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
